--- a/woorden.xlsx
+++ b/woorden.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E66734-854E-491C-84DC-741DAD534EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6286285B-3F7F-4384-9F37-C14E86D76403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6905" uniqueCount="2811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7255" uniqueCount="2945">
   <si>
     <t>de wijn</t>
   </si>
@@ -8484,6 +8484,408 @@
   </si>
   <si>
     <t>een kat</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>Van In Zouff 6</t>
+  </si>
+  <si>
+    <t>comprendre</t>
+  </si>
+  <si>
+    <t>apprendre</t>
+  </si>
+  <si>
+    <t>compter</t>
+  </si>
+  <si>
+    <t>devoir</t>
+  </si>
+  <si>
+    <t>un devoir</t>
+  </si>
+  <si>
+    <t>fermer</t>
+  </si>
+  <si>
+    <t>il faut</t>
+  </si>
+  <si>
+    <t>pouvoir</t>
+  </si>
+  <si>
+    <t>une année</t>
+  </si>
+  <si>
+    <t>demain</t>
+  </si>
+  <si>
+    <t>aujourd'hui</t>
+  </si>
+  <si>
+    <t>aujourd'hui nous sommes le …</t>
+  </si>
+  <si>
+    <t>déjà</t>
+  </si>
+  <si>
+    <t>tout de suite</t>
+  </si>
+  <si>
+    <t>contre</t>
+  </si>
+  <si>
+    <t>derrière</t>
+  </si>
+  <si>
+    <t>devant</t>
+  </si>
+  <si>
+    <t>entre</t>
+  </si>
+  <si>
+    <t>sous</t>
+  </si>
+  <si>
+    <t>sur</t>
+  </si>
+  <si>
+    <t>je prends</t>
+  </si>
+  <si>
+    <t>tu prends</t>
+  </si>
+  <si>
+    <t>il/elle/on prend</t>
+  </si>
+  <si>
+    <t>nous prenons</t>
+  </si>
+  <si>
+    <t>vous prenez</t>
+  </si>
+  <si>
+    <t>il/elles prennent</t>
+  </si>
+  <si>
+    <t>je comprends</t>
+  </si>
+  <si>
+    <t>tu comprends</t>
+  </si>
+  <si>
+    <t>il/elle/on comprend</t>
+  </si>
+  <si>
+    <t>nous comprenons</t>
+  </si>
+  <si>
+    <t>vous comprenez</t>
+  </si>
+  <si>
+    <t>ils/elles comprennent</t>
+  </si>
+  <si>
+    <t>j'apprends</t>
+  </si>
+  <si>
+    <t>tu apprends</t>
+  </si>
+  <si>
+    <t>il/elle/on apprend</t>
+  </si>
+  <si>
+    <t>nous apprenons</t>
+  </si>
+  <si>
+    <t>vous apprenez</t>
+  </si>
+  <si>
+    <t>ils/elles apprennent</t>
+  </si>
+  <si>
+    <t>je veux</t>
+  </si>
+  <si>
+    <t>tu veux</t>
+  </si>
+  <si>
+    <t>il/elle/on veut</t>
+  </si>
+  <si>
+    <t>nous voulons</t>
+  </si>
+  <si>
+    <t>vous voulez</t>
+  </si>
+  <si>
+    <t>ils/elles veulent</t>
+  </si>
+  <si>
+    <t>je peux</t>
+  </si>
+  <si>
+    <t>tu peux</t>
+  </si>
+  <si>
+    <t>il/elle/on peut</t>
+  </si>
+  <si>
+    <t>nous pouvons</t>
+  </si>
+  <si>
+    <t>vous pouvez</t>
+  </si>
+  <si>
+    <t>ils/elles peuvent</t>
+  </si>
+  <si>
+    <t>je dois</t>
+  </si>
+  <si>
+    <t>tu dois</t>
+  </si>
+  <si>
+    <t>il/elle/on doit</t>
+  </si>
+  <si>
+    <t>nous devons</t>
+  </si>
+  <si>
+    <t>vous devez</t>
+  </si>
+  <si>
+    <t>ils/elles doivent</t>
+  </si>
+  <si>
+    <t>je compte</t>
+  </si>
+  <si>
+    <t>tu comptes</t>
+  </si>
+  <si>
+    <t>il/elle/on compte</t>
+  </si>
+  <si>
+    <t>nous comptons</t>
+  </si>
+  <si>
+    <t>vous comptez</t>
+  </si>
+  <si>
+    <t>ils/elles comptent</t>
+  </si>
+  <si>
+    <t>je ferme</t>
+  </si>
+  <si>
+    <t>tu fermes</t>
+  </si>
+  <si>
+    <t>il/elle/on ferme</t>
+  </si>
+  <si>
+    <t>nous fermons</t>
+  </si>
+  <si>
+    <t>vous fermez</t>
+  </si>
+  <si>
+    <t>ils/elles ferment</t>
+  </si>
+  <si>
+    <t>leren</t>
+  </si>
+  <si>
+    <t>tellen</t>
+  </si>
+  <si>
+    <t>moeten</t>
+  </si>
+  <si>
+    <t>een huiswerk</t>
+  </si>
+  <si>
+    <t>het is nodig</t>
+  </si>
+  <si>
+    <t>vandaag is het de …</t>
+  </si>
+  <si>
+    <t>al</t>
+  </si>
+  <si>
+    <t>direct</t>
+  </si>
+  <si>
+    <t>tegen</t>
+  </si>
+  <si>
+    <t>achter</t>
+  </si>
+  <si>
+    <t>tussen</t>
+  </si>
+  <si>
+    <t>onder</t>
+  </si>
+  <si>
+    <t>op</t>
+  </si>
+  <si>
+    <t>mogen, kunnen</t>
+  </si>
+  <si>
+    <t>voor (plaats)</t>
+  </si>
+  <si>
+    <t>een jaar (tijdsduur)</t>
+  </si>
+  <si>
+    <t>ik neem</t>
+  </si>
+  <si>
+    <t>jij neemt</t>
+  </si>
+  <si>
+    <t>wij nemen</t>
+  </si>
+  <si>
+    <t>jullie nemen</t>
+  </si>
+  <si>
+    <t>wij/zij nemen</t>
+  </si>
+  <si>
+    <t>ik begrijp</t>
+  </si>
+  <si>
+    <t>jij begrijpt</t>
+  </si>
+  <si>
+    <t>wij begrijpen</t>
+  </si>
+  <si>
+    <t>jullie begrijpen</t>
+  </si>
+  <si>
+    <t>wij/zij begrijpen</t>
+  </si>
+  <si>
+    <t>ik leer</t>
+  </si>
+  <si>
+    <t>jij leert</t>
+  </si>
+  <si>
+    <t>wij leren</t>
+  </si>
+  <si>
+    <t>jullie leren</t>
+  </si>
+  <si>
+    <t>wij/zij leren</t>
+  </si>
+  <si>
+    <t>ik wil</t>
+  </si>
+  <si>
+    <t>jij wilt</t>
+  </si>
+  <si>
+    <t>wij willen</t>
+  </si>
+  <si>
+    <t>jullie willen</t>
+  </si>
+  <si>
+    <t>wij/zij willen</t>
+  </si>
+  <si>
+    <t>ik mag/kan</t>
+  </si>
+  <si>
+    <t>wij mogen/kunnen</t>
+  </si>
+  <si>
+    <t>jullie mogen/kunnen</t>
+  </si>
+  <si>
+    <t>wij/zij mogen/kunnen</t>
+  </si>
+  <si>
+    <t>hij/zij/het neemt</t>
+  </si>
+  <si>
+    <t>hij/zij/het begrijpt</t>
+  </si>
+  <si>
+    <t>hij/zij/het leert</t>
+  </si>
+  <si>
+    <t>hij/zij/het wilt</t>
+  </si>
+  <si>
+    <t>hij/zij/het mag/kan</t>
+  </si>
+  <si>
+    <t>jij mag/kan (kunt)</t>
+  </si>
+  <si>
+    <t>ik moet</t>
+  </si>
+  <si>
+    <t>jij moet</t>
+  </si>
+  <si>
+    <t>hij/zij/het moet</t>
+  </si>
+  <si>
+    <t>wij moeten</t>
+  </si>
+  <si>
+    <t>jullie moeten</t>
+  </si>
+  <si>
+    <t>wij/zij moeten</t>
+  </si>
+  <si>
+    <t>ik tel</t>
+  </si>
+  <si>
+    <t>jij telt</t>
+  </si>
+  <si>
+    <t>hij/zij/het telt</t>
+  </si>
+  <si>
+    <t>wij tellen</t>
+  </si>
+  <si>
+    <t>wij/zij tellen</t>
+  </si>
+  <si>
+    <t>jullie tellen</t>
+  </si>
+  <si>
+    <t>ik sluit</t>
+  </si>
+  <si>
+    <t>jij sluit</t>
+  </si>
+  <si>
+    <t>hij/zij/het sluit</t>
+  </si>
+  <si>
+    <t>wij sluiten</t>
+  </si>
+  <si>
+    <t>jullie sluiten</t>
+  </si>
+  <si>
+    <t>wij/zij sluiten</t>
   </si>
 </sst>
 </file>
@@ -8837,7 +9239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3604FC4-2915-4560-8271-BF036F1F45A7}">
-  <dimension ref="A1:L1093"/>
+  <dimension ref="A1:L1163"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
@@ -38305,6 +38707,1616 @@
         <v>2270</v>
       </c>
     </row>
+    <row r="1094" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1094" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1094" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1094" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1094">
+        <v>1</v>
+      </c>
+      <c r="F1094" s="4" t="s">
+        <v>2727</v>
+      </c>
+      <c r="H1094" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1095" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1095" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1095" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1095">
+        <v>2</v>
+      </c>
+      <c r="F1095" s="4" t="s">
+        <v>2813</v>
+      </c>
+      <c r="H1095" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1096" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1096" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1096" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1096">
+        <v>3</v>
+      </c>
+      <c r="F1096" s="4" t="s">
+        <v>2814</v>
+      </c>
+      <c r="H1096" t="s">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1097" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1097" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1097" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1097">
+        <v>4</v>
+      </c>
+      <c r="F1097" s="4" t="s">
+        <v>2815</v>
+      </c>
+      <c r="H1097" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1098" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1098" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1098" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1098">
+        <v>5</v>
+      </c>
+      <c r="F1098" s="4" t="s">
+        <v>2816</v>
+      </c>
+      <c r="H1098" t="s">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1099" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1099" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1099" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1099">
+        <v>6</v>
+      </c>
+      <c r="F1099" s="4" t="s">
+        <v>2817</v>
+      </c>
+      <c r="H1099" t="s">
+        <v>2884</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1100" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1100" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1100">
+        <v>7</v>
+      </c>
+      <c r="F1100" s="4" t="s">
+        <v>2818</v>
+      </c>
+      <c r="H1100" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1101" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1101" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1101">
+        <v>8</v>
+      </c>
+      <c r="F1101" s="4" t="s">
+        <v>2819</v>
+      </c>
+      <c r="H1101" t="s">
+        <v>2885</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1102" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1102" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1102">
+        <v>9</v>
+      </c>
+      <c r="F1102" s="4" t="s">
+        <v>2820</v>
+      </c>
+      <c r="H1102" t="s">
+        <v>2894</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1103" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1103" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1103" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1103">
+        <v>10</v>
+      </c>
+      <c r="F1103" s="4" t="s">
+        <v>2821</v>
+      </c>
+      <c r="H1103" t="s">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1104" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1104" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1104">
+        <v>11</v>
+      </c>
+      <c r="F1104" s="4" t="s">
+        <v>2822</v>
+      </c>
+      <c r="H1104" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1105" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1105" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1105" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1105" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1105">
+        <v>12</v>
+      </c>
+      <c r="F1105" s="4" t="s">
+        <v>2823</v>
+      </c>
+      <c r="H1105" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1106" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1106" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1106" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1106">
+        <v>13</v>
+      </c>
+      <c r="F1106" s="4" t="s">
+        <v>2824</v>
+      </c>
+      <c r="H1106" t="s">
+        <v>2886</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1107" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1107" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1107" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1107" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1107">
+        <v>14</v>
+      </c>
+      <c r="F1107" s="4" t="s">
+        <v>2825</v>
+      </c>
+      <c r="H1107" t="s">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1108" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1108" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1108" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1108" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1108">
+        <v>15</v>
+      </c>
+      <c r="F1108" s="4" t="s">
+        <v>2826</v>
+      </c>
+      <c r="H1108" t="s">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1109" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1109" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1109" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1109" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1109">
+        <v>16</v>
+      </c>
+      <c r="F1109" s="4" t="s">
+        <v>2827</v>
+      </c>
+      <c r="H1109" t="s">
+        <v>2889</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1110" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1110" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1110" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1110">
+        <v>17</v>
+      </c>
+      <c r="F1110" s="4" t="s">
+        <v>2828</v>
+      </c>
+      <c r="H1110" t="s">
+        <v>2890</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1111" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1111" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1111" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1111">
+        <v>18</v>
+      </c>
+      <c r="F1111" s="4" t="s">
+        <v>2829</v>
+      </c>
+      <c r="H1111" t="s">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1112" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1112" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1112" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1112" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1112">
+        <v>19</v>
+      </c>
+      <c r="F1112" s="4" t="s">
+        <v>2830</v>
+      </c>
+      <c r="H1112" t="s">
+        <v>2891</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1113" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1113" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1113" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1113" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1113">
+        <v>20</v>
+      </c>
+      <c r="F1113" s="4" t="s">
+        <v>2831</v>
+      </c>
+      <c r="H1113" t="s">
+        <v>2892</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1114" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1114" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1114" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1114" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1114">
+        <v>21</v>
+      </c>
+      <c r="F1114" s="4" t="s">
+        <v>2832</v>
+      </c>
+      <c r="H1114" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1115" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1115" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1115" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1115" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1115">
+        <v>22</v>
+      </c>
+      <c r="F1115" s="4" t="s">
+        <v>2833</v>
+      </c>
+      <c r="H1115" t="s">
+        <v>2897</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1116" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1116" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1116" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1116" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1116">
+        <v>23</v>
+      </c>
+      <c r="F1116" s="4" t="s">
+        <v>2834</v>
+      </c>
+      <c r="H1116" t="s">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1117" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1117" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1117" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1117" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1117">
+        <v>24</v>
+      </c>
+      <c r="F1117" s="4" t="s">
+        <v>2835</v>
+      </c>
+      <c r="H1117" t="s">
+        <v>2921</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1118" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1118" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1118" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1118" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1118">
+        <v>25</v>
+      </c>
+      <c r="F1118" s="4" t="s">
+        <v>2836</v>
+      </c>
+      <c r="H1118" t="s">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1119" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1119" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1119" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1119">
+        <v>26</v>
+      </c>
+      <c r="F1119" s="4" t="s">
+        <v>2837</v>
+      </c>
+      <c r="H1119" t="s">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1120" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1120" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1120" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1120">
+        <v>27</v>
+      </c>
+      <c r="F1120" s="4" t="s">
+        <v>2838</v>
+      </c>
+      <c r="H1120" t="s">
+        <v>2901</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1121" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1121" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1121" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1121">
+        <v>28</v>
+      </c>
+      <c r="F1121" s="4" t="s">
+        <v>2839</v>
+      </c>
+      <c r="H1121" t="s">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1122" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1122" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1122" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1122" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1122">
+        <v>29</v>
+      </c>
+      <c r="F1122" s="4" t="s">
+        <v>2840</v>
+      </c>
+      <c r="H1122" t="s">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1123" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1123" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1123" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1123" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1123">
+        <v>30</v>
+      </c>
+      <c r="F1123" s="4" t="s">
+        <v>2841</v>
+      </c>
+      <c r="H1123" t="s">
+        <v>2922</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1124" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1124" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1124" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1124" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1124">
+        <v>31</v>
+      </c>
+      <c r="F1124" s="4" t="s">
+        <v>2842</v>
+      </c>
+      <c r="H1124" t="s">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1125" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1125" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1125" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1125">
+        <v>32</v>
+      </c>
+      <c r="F1125" s="4" t="s">
+        <v>2843</v>
+      </c>
+      <c r="H1125" t="s">
+        <v>2905</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1126" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1126" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1126">
+        <v>33</v>
+      </c>
+      <c r="F1126" s="4" t="s">
+        <v>2844</v>
+      </c>
+      <c r="H1126" t="s">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1127" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1127" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1127" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1127">
+        <v>34</v>
+      </c>
+      <c r="F1127" s="4" t="s">
+        <v>2845</v>
+      </c>
+      <c r="H1127" t="s">
+        <v>2907</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1128" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1128" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1128" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1128" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1128">
+        <v>35</v>
+      </c>
+      <c r="F1128" s="4" t="s">
+        <v>2846</v>
+      </c>
+      <c r="H1128" t="s">
+        <v>2908</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1129" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1129" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1129" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1129">
+        <v>36</v>
+      </c>
+      <c r="F1129" s="4" t="s">
+        <v>2847</v>
+      </c>
+      <c r="H1129" t="s">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1130" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1130" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1130" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1130" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1130">
+        <v>37</v>
+      </c>
+      <c r="F1130" s="4" t="s">
+        <v>2848</v>
+      </c>
+      <c r="H1130" t="s">
+        <v>2909</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1131" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1131" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1131" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1131">
+        <v>38</v>
+      </c>
+      <c r="F1131" s="4" t="s">
+        <v>2849</v>
+      </c>
+      <c r="H1131" t="s">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1132" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1132" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1132" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1132">
+        <v>39</v>
+      </c>
+      <c r="F1132" s="4" t="s">
+        <v>2850</v>
+      </c>
+      <c r="H1132" t="s">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1133" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1133" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1133" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1133" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1133">
+        <v>40</v>
+      </c>
+      <c r="F1133" s="4" t="s">
+        <v>2851</v>
+      </c>
+      <c r="H1133" t="s">
+        <v>2912</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1134" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1134" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1134" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1134" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1134">
+        <v>41</v>
+      </c>
+      <c r="F1134" s="4" t="s">
+        <v>2852</v>
+      </c>
+      <c r="H1134" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1135" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1135" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1135" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1135">
+        <v>42</v>
+      </c>
+      <c r="F1135" s="4" t="s">
+        <v>2853</v>
+      </c>
+      <c r="H1135" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1136" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1136" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1136" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1136">
+        <v>43</v>
+      </c>
+      <c r="F1136" s="4" t="s">
+        <v>2854</v>
+      </c>
+      <c r="H1136" t="s">
+        <v>2914</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1137" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1137" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1137" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1137" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1137">
+        <v>44</v>
+      </c>
+      <c r="F1137" s="4" t="s">
+        <v>2855</v>
+      </c>
+      <c r="H1137" t="s">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1138" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1138" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1138" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1138">
+        <v>45</v>
+      </c>
+      <c r="F1138" s="4" t="s">
+        <v>2856</v>
+      </c>
+      <c r="H1138" t="s">
+        <v>2916</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1139" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1139" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1139" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1139">
+        <v>46</v>
+      </c>
+      <c r="F1139" s="4" t="s">
+        <v>2857</v>
+      </c>
+      <c r="H1139" t="s">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1140" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1140" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1140" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1140">
+        <v>47</v>
+      </c>
+      <c r="F1140" s="4" t="s">
+        <v>2858</v>
+      </c>
+      <c r="H1140" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1141" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1141" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1141">
+        <v>48</v>
+      </c>
+      <c r="F1141" s="4" t="s">
+        <v>2859</v>
+      </c>
+      <c r="H1141" t="s">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1142" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1142" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1142">
+        <v>49</v>
+      </c>
+      <c r="F1142" s="4" t="s">
+        <v>2860</v>
+      </c>
+      <c r="H1142" t="s">
+        <v>2918</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1143" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1143" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1143">
+        <v>50</v>
+      </c>
+      <c r="F1143" s="4" t="s">
+        <v>2861</v>
+      </c>
+      <c r="H1143" t="s">
+        <v>2919</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1144" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1144" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1144" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1144" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1144">
+        <v>51</v>
+      </c>
+      <c r="F1144" s="4" t="s">
+        <v>2862</v>
+      </c>
+      <c r="H1144" t="s">
+        <v>2920</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1145" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1145" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1145" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1145" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1145">
+        <v>52</v>
+      </c>
+      <c r="F1145" s="4" t="s">
+        <v>2863</v>
+      </c>
+      <c r="H1145" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1146" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1146" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1146">
+        <v>53</v>
+      </c>
+      <c r="F1146" s="4" t="s">
+        <v>2864</v>
+      </c>
+      <c r="H1146" t="s">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1147" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1147" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1147">
+        <v>54</v>
+      </c>
+      <c r="F1147" s="4" t="s">
+        <v>2865</v>
+      </c>
+      <c r="H1147" t="s">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1148" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1148" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1148">
+        <v>55</v>
+      </c>
+      <c r="F1148" s="4" t="s">
+        <v>2866</v>
+      </c>
+      <c r="H1148" t="s">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1149" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1149" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1149">
+        <v>56</v>
+      </c>
+      <c r="F1149" s="4" t="s">
+        <v>2867</v>
+      </c>
+      <c r="H1149" t="s">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1150" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1150" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1150">
+        <v>57</v>
+      </c>
+      <c r="F1150" s="4" t="s">
+        <v>2868</v>
+      </c>
+      <c r="H1150" t="s">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1151" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1151" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1151" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1151">
+        <v>58</v>
+      </c>
+      <c r="F1151" s="4" t="s">
+        <v>2869</v>
+      </c>
+      <c r="H1151" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1152" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1152" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1152">
+        <v>59</v>
+      </c>
+      <c r="F1152" s="4" t="s">
+        <v>2870</v>
+      </c>
+      <c r="H1152" t="s">
+        <v>2934</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1153" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1153" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1153">
+        <v>60</v>
+      </c>
+      <c r="F1153" s="4" t="s">
+        <v>2871</v>
+      </c>
+      <c r="H1153" t="s">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1154" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1154" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1154" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1154">
+        <v>61</v>
+      </c>
+      <c r="F1154" s="4" t="s">
+        <v>2872</v>
+      </c>
+      <c r="H1154" t="s">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1155" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1155" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1155" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1155">
+        <v>62</v>
+      </c>
+      <c r="F1155" s="4" t="s">
+        <v>2873</v>
+      </c>
+      <c r="H1155" t="s">
+        <v>2938</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1156" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1156" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1156" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1156">
+        <v>63</v>
+      </c>
+      <c r="F1156" s="4" t="s">
+        <v>2874</v>
+      </c>
+      <c r="H1156" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1157" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1157" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1157">
+        <v>64</v>
+      </c>
+      <c r="F1157" s="4" t="s">
+        <v>2875</v>
+      </c>
+      <c r="H1157" t="s">
+        <v>2939</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1158" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1158" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1158" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1158">
+        <v>65</v>
+      </c>
+      <c r="F1158" s="4" t="s">
+        <v>2876</v>
+      </c>
+      <c r="H1158" t="s">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1159" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1159" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1159" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1159">
+        <v>66</v>
+      </c>
+      <c r="F1159" s="4" t="s">
+        <v>2877</v>
+      </c>
+      <c r="H1159" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1160" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1160" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1160" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1160" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1160">
+        <v>67</v>
+      </c>
+      <c r="F1160" s="4" t="s">
+        <v>2878</v>
+      </c>
+      <c r="H1160" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1161" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1161" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1161" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1161">
+        <v>68</v>
+      </c>
+      <c r="F1161" s="4" t="s">
+        <v>2879</v>
+      </c>
+      <c r="H1161" t="s">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1162" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1162" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1162" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1162">
+        <v>69</v>
+      </c>
+      <c r="F1162" s="4" t="s">
+        <v>2880</v>
+      </c>
+      <c r="H1162" t="s">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1163" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1163" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1163" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1163">
+        <v>70</v>
+      </c>
+      <c r="F1163" s="4" t="s">
+        <v>2197</v>
+      </c>
+      <c r="H1163" t="s">
+        <v>1579</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/woorden.xlsx
+++ b/woorden.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6286285B-3F7F-4384-9F37-C14E86D76403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF598A6-5B8C-491E-9691-A7AEC0F6E1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="330" yWindow="2740" windowWidth="21430" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Woorden" sheetId="19" r:id="rId1"/>
@@ -39201,10 +39201,10 @@
         <v>2812</v>
       </c>
       <c r="D1115" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1115">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F1115" s="4" t="s">
         <v>2833</v>
@@ -39224,10 +39224,10 @@
         <v>2812</v>
       </c>
       <c r="D1116" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1116">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F1116" s="4" t="s">
         <v>2834</v>
@@ -39247,10 +39247,10 @@
         <v>2812</v>
       </c>
       <c r="D1117" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1117">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F1117" s="4" t="s">
         <v>2835</v>
@@ -39270,10 +39270,10 @@
         <v>2812</v>
       </c>
       <c r="D1118" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1118">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F1118" s="4" t="s">
         <v>2836</v>
@@ -39293,10 +39293,10 @@
         <v>2812</v>
       </c>
       <c r="D1119" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1119">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F1119" s="4" t="s">
         <v>2837</v>
@@ -39316,10 +39316,10 @@
         <v>2812</v>
       </c>
       <c r="D1120" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1120">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="F1120" s="4" t="s">
         <v>2838</v>
@@ -39339,10 +39339,10 @@
         <v>2812</v>
       </c>
       <c r="D1121" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1121">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F1121" s="4" t="s">
         <v>2839</v>
@@ -39362,10 +39362,10 @@
         <v>2812</v>
       </c>
       <c r="D1122" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1122">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F1122" s="4" t="s">
         <v>2840</v>
@@ -39385,10 +39385,10 @@
         <v>2812</v>
       </c>
       <c r="D1123" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1123">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F1123" s="4" t="s">
         <v>2841</v>
@@ -39408,10 +39408,10 @@
         <v>2812</v>
       </c>
       <c r="D1124" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1124">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F1124" s="4" t="s">
         <v>2842</v>
@@ -39431,10 +39431,10 @@
         <v>2812</v>
       </c>
       <c r="D1125" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1125">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F1125" s="4" t="s">
         <v>2843</v>
@@ -39454,10 +39454,10 @@
         <v>2812</v>
       </c>
       <c r="D1126" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1126">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F1126" s="4" t="s">
         <v>2844</v>
@@ -39477,10 +39477,10 @@
         <v>2812</v>
       </c>
       <c r="D1127" s="2">
+        <v>113</v>
+      </c>
+      <c r="E1127">
         <v>13</v>
-      </c>
-      <c r="E1127">
-        <v>34</v>
       </c>
       <c r="F1127" s="4" t="s">
         <v>2845</v>
@@ -39500,10 +39500,10 @@
         <v>2812</v>
       </c>
       <c r="D1128" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1128">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F1128" s="4" t="s">
         <v>2846</v>
@@ -39523,10 +39523,10 @@
         <v>2812</v>
       </c>
       <c r="D1129" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1129">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F1129" s="4" t="s">
         <v>2847</v>
@@ -39546,10 +39546,10 @@
         <v>2812</v>
       </c>
       <c r="D1130" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1130">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F1130" s="4" t="s">
         <v>2848</v>
@@ -39569,10 +39569,10 @@
         <v>2812</v>
       </c>
       <c r="D1131" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1131">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F1131" s="4" t="s">
         <v>2849</v>
@@ -39592,10 +39592,10 @@
         <v>2812</v>
       </c>
       <c r="D1132" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1132">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F1132" s="4" t="s">
         <v>2850</v>
@@ -39615,10 +39615,10 @@
         <v>2812</v>
       </c>
       <c r="D1133" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1133">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F1133" s="4" t="s">
         <v>2851</v>
@@ -39638,10 +39638,10 @@
         <v>2812</v>
       </c>
       <c r="D1134" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1134">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F1134" s="4" t="s">
         <v>2852</v>
@@ -39661,10 +39661,10 @@
         <v>2812</v>
       </c>
       <c r="D1135" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1135">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F1135" s="4" t="s">
         <v>2853</v>
@@ -39684,10 +39684,10 @@
         <v>2812</v>
       </c>
       <c r="D1136" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1136">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F1136" s="4" t="s">
         <v>2854</v>
@@ -39707,10 +39707,10 @@
         <v>2812</v>
       </c>
       <c r="D1137" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1137">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="F1137" s="4" t="s">
         <v>2855</v>
@@ -39730,10 +39730,10 @@
         <v>2812</v>
       </c>
       <c r="D1138" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1138">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F1138" s="4" t="s">
         <v>2856</v>
@@ -39753,10 +39753,10 @@
         <v>2812</v>
       </c>
       <c r="D1139" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1139">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F1139" s="4" t="s">
         <v>2857</v>
@@ -39776,10 +39776,10 @@
         <v>2812</v>
       </c>
       <c r="D1140" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1140">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F1140" s="4" t="s">
         <v>2858</v>
@@ -39799,10 +39799,10 @@
         <v>2812</v>
       </c>
       <c r="D1141" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1141">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F1141" s="4" t="s">
         <v>2859</v>
@@ -39822,10 +39822,10 @@
         <v>2812</v>
       </c>
       <c r="D1142" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1142">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="F1142" s="4" t="s">
         <v>2860</v>
@@ -39845,10 +39845,10 @@
         <v>2812</v>
       </c>
       <c r="D1143" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1143">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F1143" s="4" t="s">
         <v>2861</v>
@@ -39868,10 +39868,10 @@
         <v>2812</v>
       </c>
       <c r="D1144" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1144">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="F1144" s="4" t="s">
         <v>2862</v>
@@ -39891,10 +39891,10 @@
         <v>2812</v>
       </c>
       <c r="D1145" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1145">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="F1145" s="4" t="s">
         <v>2863</v>
@@ -39914,10 +39914,10 @@
         <v>2812</v>
       </c>
       <c r="D1146" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1146">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F1146" s="4" t="s">
         <v>2864</v>
@@ -39937,10 +39937,10 @@
         <v>2812</v>
       </c>
       <c r="D1147" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1147">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="F1147" s="4" t="s">
         <v>2865</v>
@@ -39960,10 +39960,10 @@
         <v>2812</v>
       </c>
       <c r="D1148" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1148">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F1148" s="4" t="s">
         <v>2866</v>
@@ -39983,10 +39983,10 @@
         <v>2812</v>
       </c>
       <c r="D1149" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1149">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F1149" s="4" t="s">
         <v>2867</v>
@@ -40006,10 +40006,10 @@
         <v>2812</v>
       </c>
       <c r="D1150" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1150">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="F1150" s="4" t="s">
         <v>2868</v>
@@ -40029,10 +40029,10 @@
         <v>2812</v>
       </c>
       <c r="D1151" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1151">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F1151" s="4" t="s">
         <v>2869</v>
@@ -40052,10 +40052,10 @@
         <v>2812</v>
       </c>
       <c r="D1152" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1152">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F1152" s="4" t="s">
         <v>2870</v>
@@ -40075,10 +40075,10 @@
         <v>2812</v>
       </c>
       <c r="D1153" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1153">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="F1153" s="4" t="s">
         <v>2871</v>
@@ -40098,10 +40098,10 @@
         <v>2812</v>
       </c>
       <c r="D1154" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1154">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F1154" s="4" t="s">
         <v>2872</v>
@@ -40121,10 +40121,10 @@
         <v>2812</v>
       </c>
       <c r="D1155" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1155">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F1155" s="4" t="s">
         <v>2873</v>
@@ -40144,10 +40144,10 @@
         <v>2812</v>
       </c>
       <c r="D1156" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1156">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="F1156" s="4" t="s">
         <v>2874</v>
@@ -40167,10 +40167,10 @@
         <v>2812</v>
       </c>
       <c r="D1157" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1157">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="F1157" s="4" t="s">
         <v>2875</v>
@@ -40190,10 +40190,10 @@
         <v>2812</v>
       </c>
       <c r="D1158" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1158">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="F1158" s="4" t="s">
         <v>2876</v>
@@ -40213,10 +40213,10 @@
         <v>2812</v>
       </c>
       <c r="D1159" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1159">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F1159" s="4" t="s">
         <v>2877</v>
@@ -40236,10 +40236,10 @@
         <v>2812</v>
       </c>
       <c r="D1160" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1160">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="F1160" s="4" t="s">
         <v>2878</v>
@@ -40259,10 +40259,10 @@
         <v>2812</v>
       </c>
       <c r="D1161" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1161">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F1161" s="4" t="s">
         <v>2879</v>
@@ -40282,10 +40282,10 @@
         <v>2812</v>
       </c>
       <c r="D1162" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1162">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F1162" s="4" t="s">
         <v>2880</v>
@@ -40305,10 +40305,10 @@
         <v>2812</v>
       </c>
       <c r="D1163" s="2">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E1163">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="F1163" s="4" t="s">
         <v>2197</v>

--- a/woorden.xlsx
+++ b/woorden.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF598A6-5B8C-491E-9691-A7AEC0F6E1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F912324A-6E0D-408D-AD99-2CE9509312C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="2740" windowWidth="21430" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="350" windowWidth="21430" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Woorden" sheetId="19" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7255" uniqueCount="2945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7925" uniqueCount="3157">
   <si>
     <t>de wijn</t>
   </si>
@@ -8756,9 +8756,6 @@
     <t>jullie nemen</t>
   </si>
   <si>
-    <t>wij/zij nemen</t>
-  </si>
-  <si>
     <t>ik begrijp</t>
   </si>
   <si>
@@ -8771,9 +8768,6 @@
     <t>jullie begrijpen</t>
   </si>
   <si>
-    <t>wij/zij begrijpen</t>
-  </si>
-  <si>
     <t>ik leer</t>
   </si>
   <si>
@@ -8786,9 +8780,6 @@
     <t>jullie leren</t>
   </si>
   <si>
-    <t>wij/zij leren</t>
-  </si>
-  <si>
     <t>ik wil</t>
   </si>
   <si>
@@ -8801,9 +8792,6 @@
     <t>jullie willen</t>
   </si>
   <si>
-    <t>wij/zij willen</t>
-  </si>
-  <si>
     <t>ik mag/kan</t>
   </si>
   <si>
@@ -8813,9 +8801,6 @@
     <t>jullie mogen/kunnen</t>
   </si>
   <si>
-    <t>wij/zij mogen/kunnen</t>
-  </si>
-  <si>
     <t>hij/zij/het neemt</t>
   </si>
   <si>
@@ -8849,9 +8834,6 @@
     <t>jullie moeten</t>
   </si>
   <si>
-    <t>wij/zij moeten</t>
-  </si>
-  <si>
     <t>ik tel</t>
   </si>
   <si>
@@ -8864,9 +8846,6 @@
     <t>wij tellen</t>
   </si>
   <si>
-    <t>wij/zij tellen</t>
-  </si>
-  <si>
     <t>jullie tellen</t>
   </si>
   <si>
@@ -8885,14 +8864,682 @@
     <t>jullie sluiten</t>
   </si>
   <si>
-    <t>wij/zij sluiten</t>
+    <t>le basket</t>
+  </si>
+  <si>
+    <t>le foot(ball)</t>
+  </si>
+  <si>
+    <t>la gym</t>
+  </si>
+  <si>
+    <t>nager</t>
+  </si>
+  <si>
+    <t>surfer</t>
+  </si>
+  <si>
+    <t>le tennis</t>
+  </si>
+  <si>
+    <t>le vélo</t>
+  </si>
+  <si>
+    <t>jouer à la balle</t>
+  </si>
+  <si>
+    <t>jouer au foot(ball)</t>
+  </si>
+  <si>
+    <t>jouer aux cartes</t>
+  </si>
+  <si>
+    <t>une balle</t>
+  </si>
+  <si>
+    <t>un ballon</t>
+  </si>
+  <si>
+    <t>un CD</t>
+  </si>
+  <si>
+    <t>chatter</t>
+  </si>
+  <si>
+    <t>un DVD</t>
+  </si>
+  <si>
+    <t>faire</t>
+  </si>
+  <si>
+    <t>faire du sport</t>
+  </si>
+  <si>
+    <t>gagner</t>
+  </si>
+  <si>
+    <t>j'ai gagné</t>
+  </si>
+  <si>
+    <t>l'internet</t>
+  </si>
+  <si>
+    <t>un jeu</t>
+  </si>
+  <si>
+    <t>des jeux</t>
+  </si>
+  <si>
+    <t>un match</t>
+  </si>
+  <si>
+    <t>surfer sur (l') internet</t>
+  </si>
+  <si>
+    <t>courir</t>
+  </si>
+  <si>
+    <t>bonne chance!</t>
+  </si>
+  <si>
+    <t>bravo!</t>
+  </si>
+  <si>
+    <t>un kilomètre</t>
+  </si>
+  <si>
+    <t>un mètre</t>
+  </si>
+  <si>
+    <t>het basketbal</t>
+  </si>
+  <si>
+    <t>het voetbal</t>
+  </si>
+  <si>
+    <t>het turnen</t>
+  </si>
+  <si>
+    <t>zwemmen</t>
+  </si>
+  <si>
+    <t>surfen</t>
+  </si>
+  <si>
+    <t>het tennis</t>
+  </si>
+  <si>
+    <t>het fietsen</t>
+  </si>
+  <si>
+    <t>met de bal spelen</t>
+  </si>
+  <si>
+    <t>voetballen</t>
+  </si>
+  <si>
+    <t>kaarten</t>
+  </si>
+  <si>
+    <t>een bal (klein)</t>
+  </si>
+  <si>
+    <t>een bal (groot), een ballon</t>
+  </si>
+  <si>
+    <t>een cd</t>
+  </si>
+  <si>
+    <t>chatten</t>
+  </si>
+  <si>
+    <t>een dvd</t>
+  </si>
+  <si>
+    <t>maken, doen</t>
+  </si>
+  <si>
+    <t>sporten</t>
+  </si>
+  <si>
+    <t>winnen</t>
+  </si>
+  <si>
+    <t>ik heb gewonnen</t>
+  </si>
+  <si>
+    <t>het internet</t>
+  </si>
+  <si>
+    <t>een spel</t>
+  </si>
+  <si>
+    <t>spellen</t>
+  </si>
+  <si>
+    <t>een match</t>
+  </si>
+  <si>
+    <t>surfen, surfen op het internet</t>
+  </si>
+  <si>
+    <t>Veel geluk</t>
+  </si>
+  <si>
+    <t>Bravo!</t>
+  </si>
+  <si>
+    <t>een kilometer</t>
+  </si>
+  <si>
+    <t>een meter</t>
+  </si>
+  <si>
+    <t>il/elle/on a</t>
+  </si>
+  <si>
+    <t>il/elle/on est</t>
+  </si>
+  <si>
+    <t>je cours</t>
+  </si>
+  <si>
+    <t>tu cours</t>
+  </si>
+  <si>
+    <t>il/elle/on court</t>
+  </si>
+  <si>
+    <t>nous courons</t>
+  </si>
+  <si>
+    <t>vous courez</t>
+  </si>
+  <si>
+    <t>ils/elles courent</t>
+  </si>
+  <si>
+    <t>je nage</t>
+  </si>
+  <si>
+    <t>tu nages</t>
+  </si>
+  <si>
+    <t>il/elle/on nage</t>
+  </si>
+  <si>
+    <t>nous nageons</t>
+  </si>
+  <si>
+    <t>vous nagez</t>
+  </si>
+  <si>
+    <t>ils/elles nagent</t>
+  </si>
+  <si>
+    <t>je surfe</t>
+  </si>
+  <si>
+    <t>tu surfes</t>
+  </si>
+  <si>
+    <t>il/elle/on surfe</t>
+  </si>
+  <si>
+    <t>nous surfons</t>
+  </si>
+  <si>
+    <t>vous surfez</t>
+  </si>
+  <si>
+    <t>ils/elles surfent</t>
+  </si>
+  <si>
+    <t>je joue</t>
+  </si>
+  <si>
+    <t>tu joues</t>
+  </si>
+  <si>
+    <t>il/elle/on joue</t>
+  </si>
+  <si>
+    <t>nous jouons</t>
+  </si>
+  <si>
+    <t>vous jouez</t>
+  </si>
+  <si>
+    <t>ils/elles jouent</t>
+  </si>
+  <si>
+    <t>je chatte</t>
+  </si>
+  <si>
+    <t>tu chattes</t>
+  </si>
+  <si>
+    <t>nous chattons</t>
+  </si>
+  <si>
+    <t>vous chattez</t>
+  </si>
+  <si>
+    <t>il/elle/on chatte</t>
+  </si>
+  <si>
+    <t>ils/elles chattent</t>
+  </si>
+  <si>
+    <t>je fais</t>
+  </si>
+  <si>
+    <t>tu fais</t>
+  </si>
+  <si>
+    <t>nous faisons</t>
+  </si>
+  <si>
+    <t>vous faites</t>
+  </si>
+  <si>
+    <t>il/elle/on fait</t>
+  </si>
+  <si>
+    <t>ils/elles font</t>
+  </si>
+  <si>
+    <t>je gagne</t>
+  </si>
+  <si>
+    <t>tu gagnes</t>
+  </si>
+  <si>
+    <t>nous gagnons</t>
+  </si>
+  <si>
+    <t>vous gagnez</t>
+  </si>
+  <si>
+    <t>il/elle/on gagne</t>
+  </si>
+  <si>
+    <t>ils/elles gagnent</t>
+  </si>
+  <si>
+    <t>hij/zij/het heeft</t>
+  </si>
+  <si>
+    <t>zij hebben</t>
+  </si>
+  <si>
+    <t>jullie hebben</t>
+  </si>
+  <si>
+    <t>hij/zij/het is</t>
+  </si>
+  <si>
+    <t>jullie zijn</t>
+  </si>
+  <si>
+    <t>zij zijn</t>
+  </si>
+  <si>
+    <t>zij nemen</t>
+  </si>
+  <si>
+    <t>zij begrijpen</t>
+  </si>
+  <si>
+    <t>zij leren</t>
+  </si>
+  <si>
+    <t>zij willen</t>
+  </si>
+  <si>
+    <t>zij mogen/kunnen</t>
+  </si>
+  <si>
+    <t>zij moeten</t>
+  </si>
+  <si>
+    <t>zij tellen</t>
+  </si>
+  <si>
+    <t>zij sluiten</t>
+  </si>
+  <si>
+    <t>ik loop</t>
+  </si>
+  <si>
+    <t>jij loopt</t>
+  </si>
+  <si>
+    <t>hij/zij/het loopt</t>
+  </si>
+  <si>
+    <t>wij lopen</t>
+  </si>
+  <si>
+    <t>jullie lopen</t>
+  </si>
+  <si>
+    <t>zij lopen</t>
+  </si>
+  <si>
+    <t>ik zwem</t>
+  </si>
+  <si>
+    <t>hij/zij/het zwemt</t>
+  </si>
+  <si>
+    <t>jij zwemt</t>
+  </si>
+  <si>
+    <t>wij zwemmen</t>
+  </si>
+  <si>
+    <t>jullie zwemmen</t>
+  </si>
+  <si>
+    <t>zij zwemmen</t>
+  </si>
+  <si>
+    <t>ik surf</t>
+  </si>
+  <si>
+    <t>jij surft</t>
+  </si>
+  <si>
+    <t>hij/zij/het surft</t>
+  </si>
+  <si>
+    <t>wij surfen</t>
+  </si>
+  <si>
+    <t>jullie surfen</t>
+  </si>
+  <si>
+    <t>zij surfen</t>
+  </si>
+  <si>
+    <t>ik speel</t>
+  </si>
+  <si>
+    <t>jij speelt</t>
+  </si>
+  <si>
+    <t>hij/zij/het speelt</t>
+  </si>
+  <si>
+    <t>wij spelen</t>
+  </si>
+  <si>
+    <t>jullie spelen</t>
+  </si>
+  <si>
+    <t>zij spelen</t>
+  </si>
+  <si>
+    <t>ik chat</t>
+  </si>
+  <si>
+    <t>jij chat</t>
+  </si>
+  <si>
+    <t>hij/zij/het chat</t>
+  </si>
+  <si>
+    <t>wij chatten</t>
+  </si>
+  <si>
+    <t>jullie chatten</t>
+  </si>
+  <si>
+    <t>zij chatten</t>
+  </si>
+  <si>
+    <t>ik maak/doe</t>
+  </si>
+  <si>
+    <t>jij maakt/doet</t>
+  </si>
+  <si>
+    <t>hij/zij/het maakt/doet</t>
+  </si>
+  <si>
+    <t>wij maken/doen</t>
+  </si>
+  <si>
+    <t>jullie maken/doen</t>
+  </si>
+  <si>
+    <t>zij maken/doen</t>
+  </si>
+  <si>
+    <t>ik win</t>
+  </si>
+  <si>
+    <t>jij wint</t>
+  </si>
+  <si>
+    <t>hij/zij/het wint</t>
+  </si>
+  <si>
+    <t>wij winnen</t>
+  </si>
+  <si>
+    <t>jullie winnen</t>
+  </si>
+  <si>
+    <t>zij winnen</t>
+  </si>
+  <si>
+    <t>une bouche</t>
+  </si>
+  <si>
+    <t>un bras</t>
+  </si>
+  <si>
+    <t>une dent</t>
+  </si>
+  <si>
+    <t>un doigt</t>
+  </si>
+  <si>
+    <t>un dos</t>
+  </si>
+  <si>
+    <t>un genou</t>
+  </si>
+  <si>
+    <t>des genoux</t>
+  </si>
+  <si>
+    <t>une jambe</t>
+  </si>
+  <si>
+    <t>une main</t>
+  </si>
+  <si>
+    <t>un nez</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">un </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>œil</t>
+    </r>
+  </si>
+  <si>
+    <t>des yeux</t>
+  </si>
+  <si>
+    <t>une oreille</t>
+  </si>
+  <si>
+    <t>un pied</t>
+  </si>
+  <si>
+    <t>une tête</t>
+  </si>
+  <si>
+    <t>un ventre</t>
+  </si>
+  <si>
+    <t>entendre</t>
+  </si>
+  <si>
+    <t>voir</t>
+  </si>
+  <si>
+    <t>een mond</t>
+  </si>
+  <si>
+    <t>een arm</t>
+  </si>
+  <si>
+    <t>een tand</t>
+  </si>
+  <si>
+    <t>een vinger</t>
+  </si>
+  <si>
+    <t>een rug</t>
+  </si>
+  <si>
+    <t>een knie</t>
+  </si>
+  <si>
+    <t>knieën</t>
+  </si>
+  <si>
+    <t>een been</t>
+  </si>
+  <si>
+    <t>een hand</t>
+  </si>
+  <si>
+    <t>een neus</t>
+  </si>
+  <si>
+    <t>een oog</t>
+  </si>
+  <si>
+    <t>ogen</t>
+  </si>
+  <si>
+    <t>een oor</t>
+  </si>
+  <si>
+    <t>een voet</t>
+  </si>
+  <si>
+    <t>een hoofd</t>
+  </si>
+  <si>
+    <t>een buik</t>
+  </si>
+  <si>
+    <t>J'ai les yeux (verts).</t>
+  </si>
+  <si>
+    <t>Est-ce-que (tu danses)?</t>
+  </si>
+  <si>
+    <t>horen</t>
+  </si>
+  <si>
+    <t>(Dans je)?</t>
+  </si>
+  <si>
+    <t>Ik heb (groene) ogen.</t>
+  </si>
+  <si>
+    <t>j'entends</t>
+  </si>
+  <si>
+    <t>tu entends</t>
+  </si>
+  <si>
+    <t>il/elle/on entend</t>
+  </si>
+  <si>
+    <t>nous entendons</t>
+  </si>
+  <si>
+    <t>vous entendez</t>
+  </si>
+  <si>
+    <t>ils/elles entendent</t>
+  </si>
+  <si>
+    <t>je vois</t>
+  </si>
+  <si>
+    <t>tu vois</t>
+  </si>
+  <si>
+    <t>il/elle/on voit</t>
+  </si>
+  <si>
+    <t>nous voyons</t>
+  </si>
+  <si>
+    <t>vous voyez</t>
+  </si>
+  <si>
+    <t>ils/elles voient</t>
+  </si>
+  <si>
+    <t>ik hoor</t>
+  </si>
+  <si>
+    <t>jij hoort</t>
+  </si>
+  <si>
+    <t>hij/zij/het hoort</t>
+  </si>
+  <si>
+    <t>wij horen</t>
+  </si>
+  <si>
+    <t>jullie horen</t>
+  </si>
+  <si>
+    <t>zij horen</t>
+  </si>
+  <si>
+    <t>ik zie</t>
+  </si>
+  <si>
+    <t>jij ziet</t>
+  </si>
+  <si>
+    <t>hij/zij/het ziet</t>
+  </si>
+  <si>
+    <t>wij zien</t>
+  </si>
+  <si>
+    <t>jullie zien</t>
+  </si>
+  <si>
+    <t>zij zien</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8927,6 +9574,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -9239,7 +9892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3604FC4-2915-4560-8271-BF036F1F45A7}">
-  <dimension ref="A1:L1163"/>
+  <dimension ref="A1:L1297"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
@@ -39201,16 +39854,16 @@
         <v>2812</v>
       </c>
       <c r="D1115" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1115">
         <v>1</v>
       </c>
       <c r="F1115" s="4" t="s">
-        <v>2833</v>
+        <v>2727</v>
       </c>
       <c r="H1115" t="s">
-        <v>2897</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="1116" spans="1:8" x14ac:dyDescent="0.35">
@@ -39224,16 +39877,16 @@
         <v>2812</v>
       </c>
       <c r="D1116" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F1116" s="4" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="H1116" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
     </row>
     <row r="1117" spans="1:8" x14ac:dyDescent="0.35">
@@ -39247,16 +39900,16 @@
         <v>2812</v>
       </c>
       <c r="D1117" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1117" s="4" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="H1117" t="s">
-        <v>2921</v>
+        <v>2898</v>
       </c>
     </row>
     <row r="1118" spans="1:8" x14ac:dyDescent="0.35">
@@ -39270,16 +39923,16 @@
         <v>2812</v>
       </c>
       <c r="D1118" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1118">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1118" s="4" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="H1118" t="s">
-        <v>2899</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="1119" spans="1:8" x14ac:dyDescent="0.35">
@@ -39293,16 +39946,16 @@
         <v>2812</v>
       </c>
       <c r="D1119" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1119">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1119" s="4" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="H1119" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.35">
@@ -39316,16 +39969,16 @@
         <v>2812</v>
       </c>
       <c r="D1120" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1120">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1120" s="4" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="H1120" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.35">
@@ -39339,16 +39992,16 @@
         <v>2812</v>
       </c>
       <c r="D1121" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1121">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1121" s="4" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="H1121" t="s">
-        <v>2902</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.35">
@@ -39362,16 +40015,16 @@
         <v>2812</v>
       </c>
       <c r="D1122" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1122">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1122" s="4" t="s">
-        <v>2840</v>
+        <v>2813</v>
       </c>
       <c r="H1122" t="s">
-        <v>2903</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="1123" spans="1:8" x14ac:dyDescent="0.35">
@@ -39385,16 +40038,16 @@
         <v>2812</v>
       </c>
       <c r="D1123" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1123">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F1123" s="4" t="s">
-        <v>2841</v>
+        <v>2839</v>
       </c>
       <c r="H1123" t="s">
-        <v>2922</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.35">
@@ -39408,16 +40061,16 @@
         <v>2812</v>
       </c>
       <c r="D1124" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1124">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F1124" s="4" t="s">
-        <v>2842</v>
+        <v>2840</v>
       </c>
       <c r="H1124" t="s">
-        <v>2904</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="1125" spans="1:8" x14ac:dyDescent="0.35">
@@ -39431,16 +40084,16 @@
         <v>2812</v>
       </c>
       <c r="D1125" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1125">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F1125" s="4" t="s">
-        <v>2843</v>
+        <v>2841</v>
       </c>
       <c r="H1125" t="s">
-        <v>2905</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="1126" spans="1:8" x14ac:dyDescent="0.35">
@@ -39454,16 +40107,16 @@
         <v>2812</v>
       </c>
       <c r="D1126" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1126">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F1126" s="4" t="s">
-        <v>2844</v>
+        <v>2842</v>
       </c>
       <c r="H1126" t="s">
-        <v>2906</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="1127" spans="1:8" x14ac:dyDescent="0.35">
@@ -39477,16 +40130,16 @@
         <v>2812</v>
       </c>
       <c r="D1127" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1127">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F1127" s="4" t="s">
-        <v>2845</v>
+        <v>2843</v>
       </c>
       <c r="H1127" t="s">
-        <v>2907</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="1128" spans="1:8" x14ac:dyDescent="0.35">
@@ -39500,16 +40153,16 @@
         <v>2812</v>
       </c>
       <c r="D1128" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1128">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F1128" s="4" t="s">
-        <v>2846</v>
+        <v>2844</v>
       </c>
       <c r="H1128" t="s">
-        <v>2908</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="1129" spans="1:8" x14ac:dyDescent="0.35">
@@ -39523,16 +40176,16 @@
         <v>2812</v>
       </c>
       <c r="D1129" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1129">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F1129" s="4" t="s">
-        <v>2847</v>
+        <v>2814</v>
       </c>
       <c r="H1129" t="s">
-        <v>2923</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="1130" spans="1:8" x14ac:dyDescent="0.35">
@@ -39546,16 +40199,16 @@
         <v>2812</v>
       </c>
       <c r="D1130" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1130">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F1130" s="4" t="s">
-        <v>2848</v>
+        <v>2845</v>
       </c>
       <c r="H1130" t="s">
-        <v>2909</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="1131" spans="1:8" x14ac:dyDescent="0.35">
@@ -39569,16 +40222,16 @@
         <v>2812</v>
       </c>
       <c r="D1131" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1131">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F1131" s="4" t="s">
-        <v>2849</v>
+        <v>2846</v>
       </c>
       <c r="H1131" t="s">
-        <v>2910</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="1132" spans="1:8" x14ac:dyDescent="0.35">
@@ -39592,16 +40245,16 @@
         <v>2812</v>
       </c>
       <c r="D1132" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1132">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F1132" s="4" t="s">
-        <v>2850</v>
+        <v>2847</v>
       </c>
       <c r="H1132" t="s">
-        <v>2911</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="1133" spans="1:8" x14ac:dyDescent="0.35">
@@ -39615,16 +40268,16 @@
         <v>2812</v>
       </c>
       <c r="D1133" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1133">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F1133" s="4" t="s">
-        <v>2851</v>
+        <v>2848</v>
       </c>
       <c r="H1133" t="s">
-        <v>2912</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="1134" spans="1:8" x14ac:dyDescent="0.35">
@@ -39638,16 +40291,16 @@
         <v>2812</v>
       </c>
       <c r="D1134" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1134">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F1134" s="4" t="s">
-        <v>2852</v>
+        <v>2849</v>
       </c>
       <c r="H1134" t="s">
-        <v>2913</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="1135" spans="1:8" x14ac:dyDescent="0.35">
@@ -39661,16 +40314,16 @@
         <v>2812</v>
       </c>
       <c r="D1135" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1135">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F1135" s="4" t="s">
-        <v>2853</v>
+        <v>2850</v>
       </c>
       <c r="H1135" t="s">
-        <v>2924</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="1136" spans="1:8" x14ac:dyDescent="0.35">
@@ -39684,16 +40337,16 @@
         <v>2812</v>
       </c>
       <c r="D1136" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1136">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F1136" s="4" t="s">
-        <v>2854</v>
+        <v>2197</v>
       </c>
       <c r="H1136" t="s">
-        <v>2914</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1137" spans="1:8" x14ac:dyDescent="0.35">
@@ -39707,16 +40360,16 @@
         <v>2812</v>
       </c>
       <c r="D1137" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1137">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F1137" s="4" t="s">
-        <v>2855</v>
+        <v>2851</v>
       </c>
       <c r="H1137" t="s">
-        <v>2915</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="1138" spans="1:8" x14ac:dyDescent="0.35">
@@ -39730,16 +40383,16 @@
         <v>2812</v>
       </c>
       <c r="D1138" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1138">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F1138" s="4" t="s">
-        <v>2856</v>
+        <v>2852</v>
       </c>
       <c r="H1138" t="s">
-        <v>2916</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="1139" spans="1:8" x14ac:dyDescent="0.35">
@@ -39753,16 +40406,16 @@
         <v>2812</v>
       </c>
       <c r="D1139" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1139">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F1139" s="4" t="s">
-        <v>2857</v>
+        <v>2853</v>
       </c>
       <c r="H1139" t="s">
-        <v>2917</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="1140" spans="1:8" x14ac:dyDescent="0.35">
@@ -39776,16 +40429,16 @@
         <v>2812</v>
       </c>
       <c r="D1140" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1140">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F1140" s="4" t="s">
-        <v>2858</v>
+        <v>2854</v>
       </c>
       <c r="H1140" t="s">
-        <v>2926</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="1141" spans="1:8" x14ac:dyDescent="0.35">
@@ -39799,16 +40452,16 @@
         <v>2812</v>
       </c>
       <c r="D1141" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1141">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F1141" s="4" t="s">
-        <v>2859</v>
+        <v>2855</v>
       </c>
       <c r="H1141" t="s">
-        <v>2925</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="1142" spans="1:8" x14ac:dyDescent="0.35">
@@ -39822,16 +40475,16 @@
         <v>2812</v>
       </c>
       <c r="D1142" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1142">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F1142" s="4" t="s">
-        <v>2860</v>
+        <v>2856</v>
       </c>
       <c r="H1142" t="s">
-        <v>2918</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="1143" spans="1:8" x14ac:dyDescent="0.35">
@@ -39845,16 +40498,16 @@
         <v>2812</v>
       </c>
       <c r="D1143" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1143">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F1143" s="4" t="s">
-        <v>2861</v>
+        <v>2820</v>
       </c>
       <c r="H1143" t="s">
-        <v>2919</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="1144" spans="1:8" x14ac:dyDescent="0.35">
@@ -39868,16 +40521,16 @@
         <v>2812</v>
       </c>
       <c r="D1144" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1144">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F1144" s="4" t="s">
-        <v>2862</v>
+        <v>2857</v>
       </c>
       <c r="H1144" t="s">
-        <v>2920</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="1145" spans="1:8" x14ac:dyDescent="0.35">
@@ -39891,16 +40544,16 @@
         <v>2812</v>
       </c>
       <c r="D1145" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1145">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F1145" s="4" t="s">
-        <v>2863</v>
+        <v>2858</v>
       </c>
       <c r="H1145" t="s">
-        <v>2927</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="1146" spans="1:8" x14ac:dyDescent="0.35">
@@ -39914,16 +40567,16 @@
         <v>2812</v>
       </c>
       <c r="D1146" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1146">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F1146" s="4" t="s">
-        <v>2864</v>
+        <v>2859</v>
       </c>
       <c r="H1146" t="s">
-        <v>2928</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="1147" spans="1:8" x14ac:dyDescent="0.35">
@@ -39937,16 +40590,16 @@
         <v>2812</v>
       </c>
       <c r="D1147" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1147">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F1147" s="4" t="s">
-        <v>2865</v>
+        <v>2860</v>
       </c>
       <c r="H1147" t="s">
-        <v>2929</v>
+        <v>2914</v>
       </c>
     </row>
     <row r="1148" spans="1:8" x14ac:dyDescent="0.35">
@@ -39960,16 +40613,16 @@
         <v>2812</v>
       </c>
       <c r="D1148" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1148">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F1148" s="4" t="s">
-        <v>2866</v>
+        <v>2861</v>
       </c>
       <c r="H1148" t="s">
-        <v>2930</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="1149" spans="1:8" x14ac:dyDescent="0.35">
@@ -39983,16 +40636,16 @@
         <v>2812</v>
       </c>
       <c r="D1149" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1149">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F1149" s="4" t="s">
-        <v>2867</v>
+        <v>2862</v>
       </c>
       <c r="H1149" t="s">
-        <v>2931</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.35">
@@ -40006,16 +40659,16 @@
         <v>2812</v>
       </c>
       <c r="D1150" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1150">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F1150" s="4" t="s">
-        <v>2868</v>
+        <v>2816</v>
       </c>
       <c r="H1150" t="s">
-        <v>2932</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="1151" spans="1:8" x14ac:dyDescent="0.35">
@@ -40029,16 +40682,16 @@
         <v>2812</v>
       </c>
       <c r="D1151" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1151">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F1151" s="4" t="s">
-        <v>2869</v>
+        <v>2863</v>
       </c>
       <c r="H1151" t="s">
-        <v>2933</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="1152" spans="1:8" x14ac:dyDescent="0.35">
@@ -40052,16 +40705,16 @@
         <v>2812</v>
       </c>
       <c r="D1152" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1152">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F1152" s="4" t="s">
-        <v>2870</v>
+        <v>2864</v>
       </c>
       <c r="H1152" t="s">
-        <v>2934</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.35">
@@ -40075,16 +40728,16 @@
         <v>2812</v>
       </c>
       <c r="D1153" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1153">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F1153" s="4" t="s">
-        <v>2871</v>
+        <v>2865</v>
       </c>
       <c r="H1153" t="s">
-        <v>2935</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.35">
@@ -40098,16 +40751,16 @@
         <v>2812</v>
       </c>
       <c r="D1154" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1154">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F1154" s="4" t="s">
-        <v>2872</v>
+        <v>2866</v>
       </c>
       <c r="H1154" t="s">
-        <v>2936</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="1155" spans="1:8" x14ac:dyDescent="0.35">
@@ -40121,16 +40774,16 @@
         <v>2812</v>
       </c>
       <c r="D1155" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1155">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F1155" s="4" t="s">
-        <v>2873</v>
+        <v>2867</v>
       </c>
       <c r="H1155" t="s">
-        <v>2938</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.35">
@@ -40144,16 +40797,16 @@
         <v>2812</v>
       </c>
       <c r="D1156" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1156">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F1156" s="4" t="s">
-        <v>2874</v>
+        <v>2868</v>
       </c>
       <c r="H1156" t="s">
-        <v>2937</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.35">
@@ -40167,16 +40820,16 @@
         <v>2812</v>
       </c>
       <c r="D1157" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1157">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F1157" s="4" t="s">
-        <v>2875</v>
+        <v>2815</v>
       </c>
       <c r="H1157" t="s">
-        <v>2939</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="1158" spans="1:8" x14ac:dyDescent="0.35">
@@ -40190,16 +40843,16 @@
         <v>2812</v>
       </c>
       <c r="D1158" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1158">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F1158" s="4" t="s">
-        <v>2876</v>
+        <v>2869</v>
       </c>
       <c r="H1158" t="s">
-        <v>2940</v>
+        <v>2927</v>
       </c>
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.35">
@@ -40213,16 +40866,16 @@
         <v>2812</v>
       </c>
       <c r="D1159" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1159">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F1159" s="4" t="s">
-        <v>2877</v>
+        <v>2870</v>
       </c>
       <c r="H1159" t="s">
-        <v>2941</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="1160" spans="1:8" x14ac:dyDescent="0.35">
@@ -40236,16 +40889,16 @@
         <v>2812</v>
       </c>
       <c r="D1160" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1160">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F1160" s="4" t="s">
-        <v>2878</v>
+        <v>2871</v>
       </c>
       <c r="H1160" t="s">
-        <v>2942</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.35">
@@ -40259,16 +40912,16 @@
         <v>2812</v>
       </c>
       <c r="D1161" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1161">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F1161" s="4" t="s">
-        <v>2879</v>
+        <v>2872</v>
       </c>
       <c r="H1161" t="s">
-        <v>2943</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="1162" spans="1:8" x14ac:dyDescent="0.35">
@@ -40282,16 +40935,16 @@
         <v>2812</v>
       </c>
       <c r="D1162" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1162">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F1162" s="4" t="s">
-        <v>2880</v>
+        <v>2873</v>
       </c>
       <c r="H1162" t="s">
-        <v>2944</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="1163" spans="1:8" x14ac:dyDescent="0.35">
@@ -40305,16 +40958,3098 @@
         <v>2812</v>
       </c>
       <c r="D1163" s="2">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="E1163">
+        <v>42</v>
+      </c>
+      <c r="F1163" s="4" t="s">
+        <v>2874</v>
+      </c>
+      <c r="H1163" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1164" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1164" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1164" s="2">
+        <v>130</v>
+      </c>
+      <c r="E1164">
+        <v>43</v>
+      </c>
+      <c r="F1164" s="4" t="s">
+        <v>2818</v>
+      </c>
+      <c r="H1164" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1165" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1165" s="2">
+        <v>130</v>
+      </c>
+      <c r="E1165">
+        <v>43</v>
+      </c>
+      <c r="F1165" s="4" t="s">
+        <v>2875</v>
+      </c>
+      <c r="H1165" t="s">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1166" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1166" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1166" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1166" s="2">
+        <v>130</v>
+      </c>
+      <c r="E1166">
+        <v>44</v>
+      </c>
+      <c r="F1166" s="4" t="s">
+        <v>2876</v>
+      </c>
+      <c r="H1166" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1167" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1167" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1167" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1167" s="2">
+        <v>130</v>
+      </c>
+      <c r="E1167">
+        <v>45</v>
+      </c>
+      <c r="F1167" s="4" t="s">
+        <v>2877</v>
+      </c>
+      <c r="H1167" t="s">
+        <v>2934</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1168" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1168" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1168" s="2">
+        <v>130</v>
+      </c>
+      <c r="E1168">
+        <v>46</v>
+      </c>
+      <c r="F1168" s="4" t="s">
+        <v>2878</v>
+      </c>
+      <c r="H1168" t="s">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1169" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1169" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1169" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1169" s="2">
+        <v>130</v>
+      </c>
+      <c r="E1169">
+        <v>47</v>
+      </c>
+      <c r="F1169" s="4" t="s">
+        <v>2879</v>
+      </c>
+      <c r="H1169" t="s">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1170" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1170" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1170" s="2">
+        <v>130</v>
+      </c>
+      <c r="E1170">
+        <v>48</v>
+      </c>
+      <c r="F1170" s="4" t="s">
+        <v>2880</v>
+      </c>
+      <c r="H1170" t="s">
+        <v>3051</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1171" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1171" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1171" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1171">
+        <v>1</v>
+      </c>
+      <c r="F1171" s="4" t="s">
+        <v>2937</v>
+      </c>
+      <c r="H1171" t="s">
+        <v>2966</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1172" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1172" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1172" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1172" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1172">
+        <v>2</v>
+      </c>
+      <c r="F1172" s="4" t="s">
+        <v>2938</v>
+      </c>
+      <c r="H1172" t="s">
+        <v>2967</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1173" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1173" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1173" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1173" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1173">
+        <v>3</v>
+      </c>
+      <c r="F1173" s="4" t="s">
+        <v>2939</v>
+      </c>
+      <c r="H1173" t="s">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1174" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1174" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1174" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1174" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1174">
+        <v>4</v>
+      </c>
+      <c r="F1174" s="4" t="s">
+        <v>2940</v>
+      </c>
+      <c r="H1174" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1175" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1175" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1175" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1175" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1175">
+        <v>5</v>
+      </c>
+      <c r="F1175" s="4" t="s">
+        <v>2941</v>
+      </c>
+      <c r="H1175" t="s">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1176" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1176" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1176" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1176" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1176">
+        <v>6</v>
+      </c>
+      <c r="F1176" s="4" t="s">
+        <v>2942</v>
+      </c>
+      <c r="H1176" t="s">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1177" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1177" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1177" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1177">
+        <v>7</v>
+      </c>
+      <c r="F1177" s="4" t="s">
+        <v>2943</v>
+      </c>
+      <c r="H1177" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1178" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1178" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1178" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1178">
+        <v>8</v>
+      </c>
+      <c r="F1178" s="4" t="s">
+        <v>2944</v>
+      </c>
+      <c r="H1178" t="s">
+        <v>2973</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1179" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1179" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1179" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1179">
+        <v>9</v>
+      </c>
+      <c r="F1179" s="4" t="s">
+        <v>2945</v>
+      </c>
+      <c r="H1179" t="s">
+        <v>2974</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1180" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1180" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1180" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1180">
+        <v>10</v>
+      </c>
+      <c r="F1180" s="4" t="s">
+        <v>2946</v>
+      </c>
+      <c r="H1180" t="s">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1181" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1181" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1181" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1181">
+        <v>11</v>
+      </c>
+      <c r="F1181" s="4" t="s">
+        <v>2947</v>
+      </c>
+      <c r="H1181" t="s">
+        <v>2976</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1182" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1182" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1182" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1182">
+        <v>12</v>
+      </c>
+      <c r="F1182" s="4" t="s">
+        <v>2948</v>
+      </c>
+      <c r="H1182" t="s">
+        <v>2977</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1183" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1183" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1183" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1183">
+        <v>13</v>
+      </c>
+      <c r="F1183" s="4" t="s">
+        <v>2949</v>
+      </c>
+      <c r="H1183" t="s">
+        <v>2978</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1184" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1184" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1184" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1184">
+        <v>14</v>
+      </c>
+      <c r="F1184" s="4" t="s">
+        <v>2950</v>
+      </c>
+      <c r="H1184" t="s">
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1185" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1185" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1185" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1185">
+        <v>15</v>
+      </c>
+      <c r="F1185" s="4" t="s">
+        <v>2951</v>
+      </c>
+      <c r="H1185" t="s">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1186" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1186" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1186">
+        <v>16</v>
+      </c>
+      <c r="F1186" s="4" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H1186" t="s">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1187" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1187" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1187">
+        <v>17</v>
+      </c>
+      <c r="F1187" s="4" t="s">
+        <v>2953</v>
+      </c>
+      <c r="H1187" t="s">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1188" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1188" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1188" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1188">
+        <v>18</v>
+      </c>
+      <c r="F1188" s="4" t="s">
+        <v>2954</v>
+      </c>
+      <c r="H1188" t="s">
+        <v>2983</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1189" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1189" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1189" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1189">
+        <v>19</v>
+      </c>
+      <c r="F1189" s="4" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H1189" t="s">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1190" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1190" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1190" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1190">
+        <v>20</v>
+      </c>
+      <c r="F1190" s="4" t="s">
+        <v>2956</v>
+      </c>
+      <c r="H1190" t="s">
+        <v>2985</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1191" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1191" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1191" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1191">
+        <v>21</v>
+      </c>
+      <c r="F1191" s="4" t="s">
+        <v>2957</v>
+      </c>
+      <c r="H1191" t="s">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1192" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1192" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1192" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1192">
+        <v>22</v>
+      </c>
+      <c r="F1192" s="4" t="s">
+        <v>2958</v>
+      </c>
+      <c r="H1192" t="s">
+        <v>2987</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1193" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1193" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1193" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1193">
+        <v>23</v>
+      </c>
+      <c r="F1193" s="4" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H1193" t="s">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1194" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1194" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1194" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1194">
+        <v>24</v>
+      </c>
+      <c r="F1194" s="4" t="s">
+        <v>2960</v>
+      </c>
+      <c r="H1194" t="s">
+        <v>2989</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1195" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1195" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1195">
+        <v>25</v>
+      </c>
+      <c r="F1195" s="4" t="s">
+        <v>2961</v>
+      </c>
+      <c r="H1195" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1196" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1196" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1196" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1196">
+        <v>26</v>
+      </c>
+      <c r="F1196" t="s">
+        <v>2962</v>
+      </c>
+      <c r="H1196" t="s">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1197" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1197" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1197">
+        <v>27</v>
+      </c>
+      <c r="F1197" t="s">
+        <v>2963</v>
+      </c>
+      <c r="H1197" t="s">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1198" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1198" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1198">
+        <v>28</v>
+      </c>
+      <c r="F1198" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H1198" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1199" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1199" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1199" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1199">
+        <v>29</v>
+      </c>
+      <c r="F1199" t="s">
+        <v>2964</v>
+      </c>
+      <c r="H1199" t="s">
+        <v>2992</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1200" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1200" s="2">
+        <v>14</v>
+      </c>
+      <c r="E1200">
+        <v>30</v>
+      </c>
+      <c r="F1200" t="s">
+        <v>2965</v>
+      </c>
+      <c r="H1200" t="s">
+        <v>2993</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1201" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1201" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1201">
+        <v>1</v>
+      </c>
+      <c r="F1201" t="s">
+        <v>2479</v>
+      </c>
+      <c r="H1201" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1202" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1202" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1202">
+        <v>2</v>
+      </c>
+      <c r="F1202" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H1202" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1203" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1203" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1203">
+        <v>3</v>
+      </c>
+      <c r="F1203" t="s">
+        <v>2481</v>
+      </c>
+      <c r="H1203" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1204" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1204" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1204">
+        <v>4</v>
+      </c>
+      <c r="F1204" t="s">
+        <v>2994</v>
+      </c>
+      <c r="H1204" t="s">
+        <v>3038</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1205" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1205" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1205" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1205">
+        <v>5</v>
+      </c>
+      <c r="F1205" t="s">
+        <v>2483</v>
+      </c>
+      <c r="H1205" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1206" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1206" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1206">
+        <v>6</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>2484</v>
+      </c>
+      <c r="H1206" t="s">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1207" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1207" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1207">
+        <v>7</v>
+      </c>
+      <c r="F1207" t="s">
+        <v>2485</v>
+      </c>
+      <c r="H1207" t="s">
+        <v>3039</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1208" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1208" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1208">
+        <v>8</v>
+      </c>
+      <c r="F1208" t="s">
+        <v>2311</v>
+      </c>
+      <c r="H1208" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1209" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1209" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1209">
+        <v>9</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>2323</v>
+      </c>
+      <c r="H1209" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1210" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1210" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1210">
+        <v>10</v>
+      </c>
+      <c r="F1210" t="s">
+        <v>2324</v>
+      </c>
+      <c r="H1210" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1211" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1211" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1211">
+        <v>11</v>
+      </c>
+      <c r="F1211" t="s">
+        <v>2995</v>
+      </c>
+      <c r="H1211" t="s">
+        <v>3041</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1212" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1212" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1212" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1212">
+        <v>12</v>
+      </c>
+      <c r="F1212" t="s">
+        <v>2326</v>
+      </c>
+      <c r="H1212" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1213" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1213" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1213" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1213">
+        <v>13</v>
+      </c>
+      <c r="F1213" t="s">
+        <v>2327</v>
+      </c>
+      <c r="H1213" t="s">
+        <v>3042</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1214" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1214" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1214">
+        <v>14</v>
+      </c>
+      <c r="F1214" t="s">
+        <v>2485</v>
+      </c>
+      <c r="H1214" t="s">
+        <v>3043</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1215" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1215" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1215" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1215">
+        <v>15</v>
+      </c>
+      <c r="F1215" t="s">
+        <v>2961</v>
+      </c>
+      <c r="H1215" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1216" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1216" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1216">
+        <v>16</v>
+      </c>
+      <c r="F1216" t="s">
+        <v>2996</v>
+      </c>
+      <c r="H1216" t="s">
+        <v>3052</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1217" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1217" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1217" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1217">
+        <v>17</v>
+      </c>
+      <c r="F1217" t="s">
+        <v>2997</v>
+      </c>
+      <c r="H1217" t="s">
+        <v>3053</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1218" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1218" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1218">
+        <v>18</v>
+      </c>
+      <c r="F1218" t="s">
+        <v>2998</v>
+      </c>
+      <c r="H1218" t="s">
+        <v>3054</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1219" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1219" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1219" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1219">
+        <v>19</v>
+      </c>
+      <c r="F1219" t="s">
+        <v>2999</v>
+      </c>
+      <c r="H1219" t="s">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1220" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1220" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1220">
+        <v>20</v>
+      </c>
+      <c r="F1220" t="s">
+        <v>3000</v>
+      </c>
+      <c r="H1220" t="s">
+        <v>3056</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1221" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1221" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1221">
+        <v>21</v>
+      </c>
+      <c r="F1221" t="s">
+        <v>3001</v>
+      </c>
+      <c r="H1221" t="s">
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1222" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1222" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1222" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1222">
+        <v>22</v>
+      </c>
+      <c r="F1222" t="s">
+        <v>2940</v>
+      </c>
+      <c r="H1222" t="s">
+        <v>2969</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1223" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1223" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1223" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1223">
+        <v>23</v>
+      </c>
+      <c r="F1223" t="s">
+        <v>3002</v>
+      </c>
+      <c r="H1223" t="s">
+        <v>3058</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1224" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1224" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1224" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1224">
+        <v>24</v>
+      </c>
+      <c r="F1224" t="s">
+        <v>3003</v>
+      </c>
+      <c r="H1224" t="s">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1225" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1225" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1225" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1225">
+        <v>25</v>
+      </c>
+      <c r="F1225" t="s">
+        <v>3004</v>
+      </c>
+      <c r="H1225" t="s">
+        <v>3059</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1226" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1226" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1226" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1226">
+        <v>26</v>
+      </c>
+      <c r="F1226" t="s">
+        <v>3005</v>
+      </c>
+      <c r="H1226" t="s">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1227" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1227" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1227" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1227">
+        <v>27</v>
+      </c>
+      <c r="F1227" t="s">
+        <v>3006</v>
+      </c>
+      <c r="H1227" t="s">
+        <v>3062</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1228" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1228" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1228" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1228">
+        <v>28</v>
+      </c>
+      <c r="F1228" t="s">
+        <v>3007</v>
+      </c>
+      <c r="H1228" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1229" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1229" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1229">
+        <v>29</v>
+      </c>
+      <c r="F1229" t="s">
+        <v>2941</v>
+      </c>
+      <c r="H1229" t="s">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1230" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1230" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1230" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1230">
+        <v>30</v>
+      </c>
+      <c r="F1230" t="s">
+        <v>3008</v>
+      </c>
+      <c r="H1230" t="s">
+        <v>3064</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1231" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1231" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1231" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1231">
+        <v>31</v>
+      </c>
+      <c r="F1231" t="s">
+        <v>3009</v>
+      </c>
+      <c r="H1231" t="s">
+        <v>3065</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1232" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1232" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1232" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1232">
+        <v>32</v>
+      </c>
+      <c r="F1232" t="s">
+        <v>3010</v>
+      </c>
+      <c r="H1232" t="s">
+        <v>3066</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1233" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1233" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1233" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1233">
+        <v>33</v>
+      </c>
+      <c r="F1233" t="s">
+        <v>3011</v>
+      </c>
+      <c r="H1233" t="s">
+        <v>3067</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1234" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1234" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1234" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1234">
+        <v>34</v>
+      </c>
+      <c r="F1234" t="s">
+        <v>3012</v>
+      </c>
+      <c r="H1234" t="s">
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1235" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1235" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1235">
+        <v>35</v>
+      </c>
+      <c r="F1235" t="s">
+        <v>3013</v>
+      </c>
+      <c r="H1235" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1236" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1236" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1236" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1236">
+        <v>36</v>
+      </c>
+      <c r="F1236" t="s">
+        <v>2418</v>
+      </c>
+      <c r="H1236" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1237" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1237" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1237">
+        <v>37</v>
+      </c>
+      <c r="F1237" t="s">
+        <v>3014</v>
+      </c>
+      <c r="H1237" t="s">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1238" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1238" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1238">
+        <v>38</v>
+      </c>
+      <c r="F1238" t="s">
+        <v>3015</v>
+      </c>
+      <c r="H1238" t="s">
+        <v>3071</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1239" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1239" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1239">
+        <v>39</v>
+      </c>
+      <c r="F1239" t="s">
+        <v>3016</v>
+      </c>
+      <c r="H1239" t="s">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1240" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1240" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1240">
+        <v>40</v>
+      </c>
+      <c r="F1240" t="s">
+        <v>3017</v>
+      </c>
+      <c r="H1240" t="s">
+        <v>3073</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1241" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1241" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1241">
+        <v>41</v>
+      </c>
+      <c r="F1241" t="s">
+        <v>3018</v>
+      </c>
+      <c r="H1241" t="s">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1242" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1242" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1242">
+        <v>42</v>
+      </c>
+      <c r="F1242" t="s">
+        <v>3019</v>
+      </c>
+      <c r="H1242" t="s">
+        <v>3075</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1243" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1243" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1243">
+        <v>43</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>2950</v>
+      </c>
+      <c r="H1243" t="s">
+        <v>2979</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1244" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1244" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1244">
+        <v>44</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>3020</v>
+      </c>
+      <c r="H1244" t="s">
+        <v>3076</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1245" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1245" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1245">
+        <v>45</v>
+      </c>
+      <c r="F1245" t="s">
+        <v>3021</v>
+      </c>
+      <c r="H1245" t="s">
+        <v>3077</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1246" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1246" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1246">
+        <v>46</v>
+      </c>
+      <c r="F1246" t="s">
+        <v>3024</v>
+      </c>
+      <c r="H1246" t="s">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1247" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1247" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1247">
+        <v>47</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>3022</v>
+      </c>
+      <c r="H1247" t="s">
+        <v>3079</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1248" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1248" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1248">
+        <v>48</v>
+      </c>
+      <c r="F1248" t="s">
+        <v>3023</v>
+      </c>
+      <c r="H1248" t="s">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1249" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1249" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1249">
         <v>49</v>
       </c>
-      <c r="F1163" s="4" t="s">
-        <v>2197</v>
-      </c>
-      <c r="H1163" t="s">
-        <v>1579</v>
+      <c r="F1249" t="s">
+        <v>3025</v>
+      </c>
+      <c r="H1249" t="s">
+        <v>3081</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1250" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1250" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1250">
+        <v>50</v>
+      </c>
+      <c r="F1250" t="s">
+        <v>2952</v>
+      </c>
+      <c r="H1250" t="s">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1251" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1251" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1251">
+        <v>51</v>
+      </c>
+      <c r="F1251" t="s">
+        <v>3026</v>
+      </c>
+      <c r="H1251" t="s">
+        <v>3082</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1252" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1252" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1252">
+        <v>52</v>
+      </c>
+      <c r="F1252" t="s">
+        <v>3027</v>
+      </c>
+      <c r="H1252" t="s">
+        <v>3083</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1253" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1253" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1253">
+        <v>53</v>
+      </c>
+      <c r="F1253" t="s">
+        <v>3030</v>
+      </c>
+      <c r="H1253" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1254" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1254" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1254">
+        <v>54</v>
+      </c>
+      <c r="F1254" t="s">
+        <v>3028</v>
+      </c>
+      <c r="H1254" t="s">
+        <v>3085</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1255" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1255" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1255">
+        <v>55</v>
+      </c>
+      <c r="F1255" t="s">
+        <v>3029</v>
+      </c>
+      <c r="H1255" t="s">
+        <v>3086</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1256" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1256" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1256">
+        <v>56</v>
+      </c>
+      <c r="F1256" t="s">
+        <v>3031</v>
+      </c>
+      <c r="H1256" t="s">
+        <v>3087</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1257" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1257" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1257">
+        <v>57</v>
+      </c>
+      <c r="F1257" t="s">
+        <v>2954</v>
+      </c>
+      <c r="H1257" t="s">
+        <v>2983</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1258" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1258" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1258">
+        <v>58</v>
+      </c>
+      <c r="F1258" t="s">
+        <v>3032</v>
+      </c>
+      <c r="H1258" t="s">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1259" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1259" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1259">
+        <v>59</v>
+      </c>
+      <c r="F1259" t="s">
+        <v>3033</v>
+      </c>
+      <c r="H1259" t="s">
+        <v>3089</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1260" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1260" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1260">
+        <v>60</v>
+      </c>
+      <c r="F1260" t="s">
+        <v>3036</v>
+      </c>
+      <c r="H1260" t="s">
+        <v>3090</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1261" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1261" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1261">
+        <v>61</v>
+      </c>
+      <c r="F1261" t="s">
+        <v>3034</v>
+      </c>
+      <c r="H1261" t="s">
+        <v>3091</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1262" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1262" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1262">
+        <v>62</v>
+      </c>
+      <c r="F1262" t="s">
+        <v>3035</v>
+      </c>
+      <c r="H1262" t="s">
+        <v>3092</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1263" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1263" s="2">
+        <v>140</v>
+      </c>
+      <c r="E1263">
+        <v>63</v>
+      </c>
+      <c r="F1263" t="s">
+        <v>3037</v>
+      </c>
+      <c r="H1263" t="s">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1264" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1264" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1264">
+        <v>1</v>
+      </c>
+      <c r="F1264" t="s">
+        <v>3128</v>
+      </c>
+      <c r="H1264" t="s">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1265" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1265" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1265">
+        <v>2</v>
+      </c>
+      <c r="F1265" t="s">
+        <v>3094</v>
+      </c>
+      <c r="H1265" t="s">
+        <v>3112</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1266" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1266" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1266">
+        <v>3</v>
+      </c>
+      <c r="F1266" t="s">
+        <v>3095</v>
+      </c>
+      <c r="H1266" t="s">
+        <v>3113</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1267" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1267" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1267">
+        <v>4</v>
+      </c>
+      <c r="F1267" t="s">
+        <v>3096</v>
+      </c>
+      <c r="H1267" t="s">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1268" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1268" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1268">
+        <v>5</v>
+      </c>
+      <c r="F1268" t="s">
+        <v>3097</v>
+      </c>
+      <c r="H1268" t="s">
+        <v>3115</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1269" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1269" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1269">
+        <v>6</v>
+      </c>
+      <c r="F1269" t="s">
+        <v>3098</v>
+      </c>
+      <c r="H1269" t="s">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1270" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1270" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1270">
+        <v>7</v>
+      </c>
+      <c r="F1270" t="s">
+        <v>3099</v>
+      </c>
+      <c r="H1270" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1271" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1271" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1271">
+        <v>8</v>
+      </c>
+      <c r="F1271" t="s">
+        <v>3100</v>
+      </c>
+      <c r="H1271" t="s">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1272" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1272" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1272">
+        <v>9</v>
+      </c>
+      <c r="F1272" t="s">
+        <v>3101</v>
+      </c>
+      <c r="H1272" t="s">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1273" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1273" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1273">
+        <v>10</v>
+      </c>
+      <c r="F1273" t="s">
+        <v>3102</v>
+      </c>
+      <c r="H1273" t="s">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1274" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1274" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1274">
+        <v>11</v>
+      </c>
+      <c r="F1274" t="s">
+        <v>3103</v>
+      </c>
+      <c r="H1274" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1275" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1275" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1275">
+        <v>12</v>
+      </c>
+      <c r="F1275" t="s">
+        <v>3104</v>
+      </c>
+      <c r="H1275" t="s">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1276" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1276" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1276">
+        <v>13</v>
+      </c>
+      <c r="F1276" t="s">
+        <v>3105</v>
+      </c>
+      <c r="H1276" t="s">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1277" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1277" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1277">
+        <v>14</v>
+      </c>
+      <c r="F1277" t="s">
+        <v>3106</v>
+      </c>
+      <c r="H1277" t="s">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1278" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1278" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1278">
+        <v>15</v>
+      </c>
+      <c r="F1278" t="s">
+        <v>3107</v>
+      </c>
+      <c r="H1278" t="s">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1279" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1279" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1279">
+        <v>16</v>
+      </c>
+      <c r="F1279" t="s">
+        <v>3108</v>
+      </c>
+      <c r="H1279" t="s">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1280" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1280" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1280">
+        <v>17</v>
+      </c>
+      <c r="F1280" t="s">
+        <v>3109</v>
+      </c>
+      <c r="H1280" t="s">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1281" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1281" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1281">
+        <v>18</v>
+      </c>
+      <c r="F1281" t="s">
+        <v>3110</v>
+      </c>
+      <c r="H1281" t="s">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1282" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1282" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1282">
+        <v>19</v>
+      </c>
+      <c r="F1282" t="s">
+        <v>3111</v>
+      </c>
+      <c r="H1282" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1283" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1283" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1283">
+        <v>20</v>
+      </c>
+      <c r="F1283" t="s">
+        <v>3129</v>
+      </c>
+      <c r="H1283" t="s">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1284" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1284" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1284">
+        <v>1</v>
+      </c>
+      <c r="F1284" t="s">
+        <v>3110</v>
+      </c>
+      <c r="H1284" t="s">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1285" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1285" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1285" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1285">
+        <v>2</v>
+      </c>
+      <c r="F1285" t="s">
+        <v>3133</v>
+      </c>
+      <c r="H1285" t="s">
+        <v>3145</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1286" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1286" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1286">
+        <v>3</v>
+      </c>
+      <c r="F1286" t="s">
+        <v>3134</v>
+      </c>
+      <c r="H1286" t="s">
+        <v>3146</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1287" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1287" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1287">
+        <v>4</v>
+      </c>
+      <c r="F1287" t="s">
+        <v>3135</v>
+      </c>
+      <c r="H1287" t="s">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1288" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1288" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1288">
+        <v>5</v>
+      </c>
+      <c r="F1288" t="s">
+        <v>3136</v>
+      </c>
+      <c r="H1288" t="s">
+        <v>3148</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1289" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1289" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1289" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1289">
+        <v>6</v>
+      </c>
+      <c r="F1289" t="s">
+        <v>3137</v>
+      </c>
+      <c r="H1289" t="s">
+        <v>3149</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1290" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1290" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1290" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1290">
+        <v>7</v>
+      </c>
+      <c r="F1290" t="s">
+        <v>3138</v>
+      </c>
+      <c r="H1290" t="s">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1291" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1291" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1291" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1291">
+        <v>8</v>
+      </c>
+      <c r="F1291" t="s">
+        <v>3111</v>
+      </c>
+      <c r="H1291" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1292" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1292" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1292">
+        <v>9</v>
+      </c>
+      <c r="F1292" t="s">
+        <v>3139</v>
+      </c>
+      <c r="H1292" t="s">
+        <v>3151</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1293" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1293" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1293" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1293">
+        <v>10</v>
+      </c>
+      <c r="F1293" t="s">
+        <v>3140</v>
+      </c>
+      <c r="H1293" t="s">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1294" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1294" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1294" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1294">
+        <v>11</v>
+      </c>
+      <c r="F1294" t="s">
+        <v>3141</v>
+      </c>
+      <c r="H1294" t="s">
+        <v>3153</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1295" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1295" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1295">
+        <v>12</v>
+      </c>
+      <c r="F1295" t="s">
+        <v>3142</v>
+      </c>
+      <c r="H1295" t="s">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1296" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1296" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1296">
+        <v>13</v>
+      </c>
+      <c r="F1296" t="s">
+        <v>3143</v>
+      </c>
+      <c r="H1296" t="s">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1297" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1297" s="2">
+        <v>150</v>
+      </c>
+      <c r="E1297">
+        <v>14</v>
+      </c>
+      <c r="F1297" t="s">
+        <v>3144</v>
+      </c>
+      <c r="H1297" t="s">
+        <v>3156</v>
       </c>
     </row>
   </sheetData>

--- a/woorden.xlsx
+++ b/woorden.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wim\Documents\Kids\Elin\SJT\Latin-quiz-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F912324A-6E0D-408D-AD99-2CE9509312C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5A4519-2870-4BCC-A688-AB4910D2168A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="350" windowWidth="21430" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3320" yWindow="600" windowWidth="21430" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Woorden" sheetId="19" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7925" uniqueCount="3157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8200" uniqueCount="3253">
   <si>
     <t>de wijn</t>
   </si>
@@ -9533,6 +9533,294 @@
   </si>
   <si>
     <t>zij zien</t>
+  </si>
+  <si>
+    <t>parce que</t>
+  </si>
+  <si>
+    <t>dire</t>
+  </si>
+  <si>
+    <t>l'automne</t>
+  </si>
+  <si>
+    <t>en automne</t>
+  </si>
+  <si>
+    <t>l'été</t>
+  </si>
+  <si>
+    <t>en été</t>
+  </si>
+  <si>
+    <t>l'hiver</t>
+  </si>
+  <si>
+    <t>en hiver</t>
+  </si>
+  <si>
+    <t>le printemps</t>
+  </si>
+  <si>
+    <t>au printemps</t>
+  </si>
+  <si>
+    <t>la neige</t>
+  </si>
+  <si>
+    <t>le soleil</t>
+  </si>
+  <si>
+    <t>le vent</t>
+  </si>
+  <si>
+    <t>chaud, chaude</t>
+  </si>
+  <si>
+    <t>froid, froide</t>
+  </si>
+  <si>
+    <t>mauvais, mauvaise</t>
+  </si>
+  <si>
+    <t>il fait beau</t>
+  </si>
+  <si>
+    <t>il fait chaud</t>
+  </si>
+  <si>
+    <t>il fait froid</t>
+  </si>
+  <si>
+    <t>il fait mauvais</t>
+  </si>
+  <si>
+    <t>il neige</t>
+  </si>
+  <si>
+    <t>il pleut</t>
+  </si>
+  <si>
+    <t>il va neiger</t>
+  </si>
+  <si>
+    <t>il va pleuvoir</t>
+  </si>
+  <si>
+    <t>il y a du soleil</t>
+  </si>
+  <si>
+    <t>il y a du vent</t>
+  </si>
+  <si>
+    <t>Quel temps fait-il?</t>
+  </si>
+  <si>
+    <t>je dis</t>
+  </si>
+  <si>
+    <t>tu dis</t>
+  </si>
+  <si>
+    <t>il/elle/on dit</t>
+  </si>
+  <si>
+    <t>nous disons</t>
+  </si>
+  <si>
+    <t>vous dites</t>
+  </si>
+  <si>
+    <t>ils/elles disent</t>
+  </si>
+  <si>
+    <t>omdat / want</t>
+  </si>
+  <si>
+    <t>zeggen</t>
+  </si>
+  <si>
+    <t>de herfst</t>
+  </si>
+  <si>
+    <t>in de herfst</t>
+  </si>
+  <si>
+    <t>in de zomer</t>
+  </si>
+  <si>
+    <t>in de winder</t>
+  </si>
+  <si>
+    <t>de lente</t>
+  </si>
+  <si>
+    <t>in de lente</t>
+  </si>
+  <si>
+    <t>de sneeuw</t>
+  </si>
+  <si>
+    <t>koud</t>
+  </si>
+  <si>
+    <t>het is mooi weer</t>
+  </si>
+  <si>
+    <t>het is warm</t>
+  </si>
+  <si>
+    <t>het is koud</t>
+  </si>
+  <si>
+    <t>het is slecht weer</t>
+  </si>
+  <si>
+    <t>het sneeuwt</t>
+  </si>
+  <si>
+    <t>het regent</t>
+  </si>
+  <si>
+    <t>het gaat sneeuwen</t>
+  </si>
+  <si>
+    <t>het gaat regenen</t>
+  </si>
+  <si>
+    <t>de zon schijnt / er is zon</t>
+  </si>
+  <si>
+    <t>het waait / er is wind</t>
+  </si>
+  <si>
+    <t>het weer</t>
+  </si>
+  <si>
+    <t>Wat voor weer is het?</t>
+  </si>
+  <si>
+    <t>ik zeg</t>
+  </si>
+  <si>
+    <t>jij zegt</t>
+  </si>
+  <si>
+    <t>hij/zij/het zegt</t>
+  </si>
+  <si>
+    <t>wij zeggen</t>
+  </si>
+  <si>
+    <t>jullie zeggen</t>
+  </si>
+  <si>
+    <t>zij zeggen</t>
+  </si>
+  <si>
+    <t>une promenade</t>
+  </si>
+  <si>
+    <t>ne … jamais</t>
+  </si>
+  <si>
+    <t>un arbre</t>
+  </si>
+  <si>
+    <t>un cheval</t>
+  </si>
+  <si>
+    <t>un cochon</t>
+  </si>
+  <si>
+    <t>un coq</t>
+  </si>
+  <si>
+    <t>une fleur</t>
+  </si>
+  <si>
+    <t>un oiseau</t>
+  </si>
+  <si>
+    <t>des oiseaux</t>
+  </si>
+  <si>
+    <t>une poule</t>
+  </si>
+  <si>
+    <t>une vache</t>
+  </si>
+  <si>
+    <t>un animal</t>
+  </si>
+  <si>
+    <t>des animaux</t>
+  </si>
+  <si>
+    <t>la campagne</t>
+  </si>
+  <si>
+    <t>un bois</t>
+  </si>
+  <si>
+    <t>la mer</t>
+  </si>
+  <si>
+    <t>une montagne</t>
+  </si>
+  <si>
+    <t>la nature</t>
+  </si>
+  <si>
+    <t>een wandeling</t>
+  </si>
+  <si>
+    <t>een boom</t>
+  </si>
+  <si>
+    <t>een paard</t>
+  </si>
+  <si>
+    <t>een varken</t>
+  </si>
+  <si>
+    <t>een haan</t>
+  </si>
+  <si>
+    <t>een blad/blaadje</t>
+  </si>
+  <si>
+    <t>een bloem</t>
+  </si>
+  <si>
+    <t>een vogel</t>
+  </si>
+  <si>
+    <t>vogels</t>
+  </si>
+  <si>
+    <t>een kip</t>
+  </si>
+  <si>
+    <t>een koe</t>
+  </si>
+  <si>
+    <t>een dier</t>
+  </si>
+  <si>
+    <t>dieren</t>
+  </si>
+  <si>
+    <t>het platteland</t>
+  </si>
+  <si>
+    <t>een bos/woud</t>
+  </si>
+  <si>
+    <t>een berg</t>
+  </si>
+  <si>
+    <t>de natuur</t>
   </si>
 </sst>
 </file>
@@ -9892,7 +10180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3604FC4-2915-4560-8271-BF036F1F45A7}">
-  <dimension ref="A1:L1297"/>
+  <dimension ref="A1:L1352"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
@@ -44052,6 +44340,1271 @@
         <v>3156</v>
       </c>
     </row>
+    <row r="1298" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1298" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1298" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1298">
+        <v>1</v>
+      </c>
+      <c r="F1298" t="s">
+        <v>3157</v>
+      </c>
+      <c r="H1298" t="s">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1299" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1299" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1299">
+        <v>2</v>
+      </c>
+      <c r="F1299" t="s">
+        <v>3158</v>
+      </c>
+      <c r="H1299" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1300" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1300" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1300">
+        <v>3</v>
+      </c>
+      <c r="F1300" t="s">
+        <v>3159</v>
+      </c>
+      <c r="H1300" t="s">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1301" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1301" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1301" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1301">
+        <v>4</v>
+      </c>
+      <c r="F1301" t="s">
+        <v>3160</v>
+      </c>
+      <c r="H1301" t="s">
+        <v>3193</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1302" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1302" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1302" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1302">
+        <v>5</v>
+      </c>
+      <c r="F1302" t="s">
+        <v>3161</v>
+      </c>
+      <c r="H1302" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1303" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1303" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1303" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1303">
+        <v>6</v>
+      </c>
+      <c r="F1303" t="s">
+        <v>3162</v>
+      </c>
+      <c r="H1303" t="s">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1304" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1304" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1304">
+        <v>7</v>
+      </c>
+      <c r="F1304" t="s">
+        <v>3163</v>
+      </c>
+      <c r="H1304" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1305" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1305" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1305" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1305">
+        <v>8</v>
+      </c>
+      <c r="F1305" t="s">
+        <v>3164</v>
+      </c>
+      <c r="H1305" t="s">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1306" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1306" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1306" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1306">
+        <v>9</v>
+      </c>
+      <c r="F1306" t="s">
+        <v>3165</v>
+      </c>
+      <c r="H1306" t="s">
+        <v>3196</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1307" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1307" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1307" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1307">
+        <v>10</v>
+      </c>
+      <c r="F1307" t="s">
+        <v>3166</v>
+      </c>
+      <c r="H1307" t="s">
+        <v>3197</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1308" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1308" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1308" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1308">
+        <v>11</v>
+      </c>
+      <c r="F1308" t="s">
+        <v>3167</v>
+      </c>
+      <c r="H1308" t="s">
+        <v>3198</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1309" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1309" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1309" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1309">
+        <v>12</v>
+      </c>
+      <c r="F1309" t="s">
+        <v>3168</v>
+      </c>
+      <c r="H1309" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1310" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1310" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1310">
+        <v>13</v>
+      </c>
+      <c r="F1310" t="s">
+        <v>3169</v>
+      </c>
+      <c r="H1310" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1311" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1311" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1311">
+        <v>14</v>
+      </c>
+      <c r="F1311" t="s">
+        <v>3170</v>
+      </c>
+      <c r="H1311" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1312" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1312" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1312">
+        <v>15</v>
+      </c>
+      <c r="F1312" t="s">
+        <v>3171</v>
+      </c>
+      <c r="H1312" t="s">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1313" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1313" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1313">
+        <v>16</v>
+      </c>
+      <c r="F1313" t="s">
+        <v>3172</v>
+      </c>
+      <c r="H1313" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1314" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1314" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1314" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1314">
+        <v>17</v>
+      </c>
+      <c r="F1314" t="s">
+        <v>3173</v>
+      </c>
+      <c r="H1314" t="s">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1315" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1315" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1315">
+        <v>18</v>
+      </c>
+      <c r="F1315" t="s">
+        <v>3174</v>
+      </c>
+      <c r="H1315" t="s">
+        <v>3201</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1316" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1316" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1316">
+        <v>19</v>
+      </c>
+      <c r="F1316" t="s">
+        <v>3175</v>
+      </c>
+      <c r="H1316" t="s">
+        <v>3202</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1317" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1317" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1317">
+        <v>20</v>
+      </c>
+      <c r="F1317" t="s">
+        <v>3176</v>
+      </c>
+      <c r="H1317" t="s">
+        <v>3203</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1318" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1318" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1318">
+        <v>21</v>
+      </c>
+      <c r="F1318" t="s">
+        <v>3177</v>
+      </c>
+      <c r="H1318" t="s">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1319" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1319" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1319">
+        <v>22</v>
+      </c>
+      <c r="F1319" t="s">
+        <v>3178</v>
+      </c>
+      <c r="H1319" t="s">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1320" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1320" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1320">
+        <v>23</v>
+      </c>
+      <c r="F1320" t="s">
+        <v>3179</v>
+      </c>
+      <c r="H1320" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1321" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1321" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1321" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1321">
+        <v>24</v>
+      </c>
+      <c r="F1321" t="s">
+        <v>3180</v>
+      </c>
+      <c r="H1321" t="s">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1322" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1322" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1322">
+        <v>25</v>
+      </c>
+      <c r="F1322" t="s">
+        <v>3181</v>
+      </c>
+      <c r="H1322" t="s">
+        <v>3208</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1323" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1323" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1323" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1323">
+        <v>26</v>
+      </c>
+      <c r="F1323" t="s">
+        <v>3182</v>
+      </c>
+      <c r="H1323" t="s">
+        <v>3209</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1324" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1324" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1324">
+        <v>27</v>
+      </c>
+      <c r="F1324" t="s">
+        <v>2157</v>
+      </c>
+      <c r="H1324" t="s">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1325" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1325" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1325">
+        <v>28</v>
+      </c>
+      <c r="F1325" t="s">
+        <v>3183</v>
+      </c>
+      <c r="H1325" t="s">
+        <v>3211</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1326" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1326" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1326" s="2">
+        <v>160</v>
+      </c>
+      <c r="E1326">
+        <v>1</v>
+      </c>
+      <c r="F1326" t="s">
+        <v>3158</v>
+      </c>
+      <c r="H1326" t="s">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1327" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1327" s="2">
+        <v>160</v>
+      </c>
+      <c r="E1327">
+        <v>2</v>
+      </c>
+      <c r="F1327" t="s">
+        <v>3184</v>
+      </c>
+      <c r="H1327" t="s">
+        <v>3212</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1328" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1328" s="2">
+        <v>160</v>
+      </c>
+      <c r="E1328">
+        <v>3</v>
+      </c>
+      <c r="F1328" t="s">
+        <v>3185</v>
+      </c>
+      <c r="H1328" t="s">
+        <v>3213</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1329" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1329" s="2">
+        <v>160</v>
+      </c>
+      <c r="E1329">
+        <v>4</v>
+      </c>
+      <c r="F1329" t="s">
+        <v>3186</v>
+      </c>
+      <c r="H1329" t="s">
+        <v>3214</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1330" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1330" s="2">
+        <v>160</v>
+      </c>
+      <c r="E1330">
+        <v>5</v>
+      </c>
+      <c r="F1330" t="s">
+        <v>3187</v>
+      </c>
+      <c r="H1330" t="s">
+        <v>3215</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1331" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1331" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1331" s="2">
+        <v>160</v>
+      </c>
+      <c r="E1331">
+        <v>6</v>
+      </c>
+      <c r="F1331" t="s">
+        <v>3188</v>
+      </c>
+      <c r="H1331" t="s">
+        <v>3216</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1332" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1332" s="2">
+        <v>160</v>
+      </c>
+      <c r="E1332">
+        <v>7</v>
+      </c>
+      <c r="F1332" t="s">
+        <v>3189</v>
+      </c>
+      <c r="H1332" t="s">
+        <v>3217</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1333" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1333" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1333">
+        <v>1</v>
+      </c>
+      <c r="F1333" t="s">
+        <v>3218</v>
+      </c>
+      <c r="H1333" t="s">
+        <v>3236</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1334" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1334" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1334">
+        <v>2</v>
+      </c>
+      <c r="F1334" t="s">
+        <v>3219</v>
+      </c>
+      <c r="H1334" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1335" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1335" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1335">
+        <v>3</v>
+      </c>
+      <c r="F1335" t="s">
+        <v>3220</v>
+      </c>
+      <c r="H1335" t="s">
+        <v>3237</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1336" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1336" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1336">
+        <v>4</v>
+      </c>
+      <c r="F1336" t="s">
+        <v>3221</v>
+      </c>
+      <c r="H1336" t="s">
+        <v>3238</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1337" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1337" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1337">
+        <v>5</v>
+      </c>
+      <c r="F1337" t="s">
+        <v>3222</v>
+      </c>
+      <c r="H1337" t="s">
+        <v>3239</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1338" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1338" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1338" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1338">
+        <v>6</v>
+      </c>
+      <c r="F1338" t="s">
+        <v>3223</v>
+      </c>
+      <c r="H1338" t="s">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1339" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1339" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1339">
+        <v>7</v>
+      </c>
+      <c r="F1339" t="s">
+        <v>2349</v>
+      </c>
+      <c r="H1339" t="s">
+        <v>3241</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1340" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1340" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1340" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1340">
+        <v>8</v>
+      </c>
+      <c r="F1340" t="s">
+        <v>3224</v>
+      </c>
+      <c r="H1340" t="s">
+        <v>3242</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1341" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1341" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1341" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1341">
+        <v>9</v>
+      </c>
+      <c r="F1341" t="s">
+        <v>3225</v>
+      </c>
+      <c r="H1341" t="s">
+        <v>3243</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1342" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1342" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1342" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1342">
+        <v>10</v>
+      </c>
+      <c r="F1342" t="s">
+        <v>3226</v>
+      </c>
+      <c r="H1342" t="s">
+        <v>3244</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1343" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1343" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1343">
+        <v>11</v>
+      </c>
+      <c r="F1343" t="s">
+        <v>3227</v>
+      </c>
+      <c r="H1343" t="s">
+        <v>3245</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1344" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1344" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1344" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1344">
+        <v>12</v>
+      </c>
+      <c r="F1344" t="s">
+        <v>3228</v>
+      </c>
+      <c r="H1344" t="s">
+        <v>3246</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1345" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1345" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1345" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1345">
+        <v>13</v>
+      </c>
+      <c r="F1345" t="s">
+        <v>3229</v>
+      </c>
+      <c r="H1345" t="s">
+        <v>3247</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1346" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1346" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1346" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1346">
+        <v>14</v>
+      </c>
+      <c r="F1346" t="s">
+        <v>3230</v>
+      </c>
+      <c r="H1346" t="s">
+        <v>3248</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1347" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1347" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1347" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1347">
+        <v>15</v>
+      </c>
+      <c r="F1347" t="s">
+        <v>3231</v>
+      </c>
+      <c r="H1347" t="s">
+        <v>3249</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1348" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1348" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1348" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1348">
+        <v>16</v>
+      </c>
+      <c r="F1348" t="s">
+        <v>3232</v>
+      </c>
+      <c r="H1348" t="s">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1349" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1349" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1349" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1349">
+        <v>17</v>
+      </c>
+      <c r="F1349" t="s">
+        <v>2717</v>
+      </c>
+      <c r="H1349" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1350" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1350" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1350" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1350">
+        <v>18</v>
+      </c>
+      <c r="F1350" t="s">
+        <v>3233</v>
+      </c>
+      <c r="H1350" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1351" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1351" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1351" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1351">
+        <v>19</v>
+      </c>
+      <c r="F1351" t="s">
+        <v>3234</v>
+      </c>
+      <c r="H1351" t="s">
+        <v>3251</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1352" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D1352" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1352">
+        <v>20</v>
+      </c>
+      <c r="F1352" t="s">
+        <v>3235</v>
+      </c>
+      <c r="H1352" t="s">
+        <v>3252</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
